--- a/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
+++ b/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekin\Desktop\FDN\kalori\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BFF644-F1E8-4E82-824F-F85C1CCD9464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB54609-98C3-41C5-908F-6886EA15291E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ozet Dashboard" sheetId="1" r:id="rId1"/>
@@ -2460,10 +2460,13 @@
     <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -2471,16 +2474,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2894,7 +2894,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="29"/>
@@ -2904,7 +2904,7 @@
       <c r="F1" s="29"/>
     </row>
     <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="29"/>
@@ -2922,181 +2922,181 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
     </row>
     <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
     </row>
     <row r="7" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
     </row>
     <row r="8" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
     </row>
     <row r="10" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
     </row>
     <row r="11" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
     </row>
     <row r="12" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
     </row>
     <row r="13" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
     </row>
     <row r="14" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
     </row>
     <row r="15" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
     </row>
     <row r="16" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
     </row>
     <row r="17" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
     </row>
     <row r="18" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
     </row>
     <row r="19" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -3137,11 +3137,11 @@
       </c>
       <c r="D23" s="6">
         <f>SUMIFS('Sprint Plani'!$H$4:$H$64,'Sprint Plani'!$A$4:$A$64,$A23,'Sprint Plani'!$K$4:$K$64,"Tamamlandı")</f>
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="E23" s="7">
         <f>IFERROR($D23/$C23,0)</f>
-        <v>0.25</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>41</v>
@@ -3209,11 +3209,11 @@
       </c>
       <c r="D26" s="10">
         <f>SUM(D23:D25)</f>
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="E26" s="11">
         <f>IFERROR(D26/C26,0)</f>
-        <v>7.1428571428571425E-2</v>
+        <v>0.13095238095238096</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>47</v>
@@ -3498,7 +3498,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="34" t="s">
         <v>81</v>
       </c>
       <c r="B46" s="29"/>
@@ -3508,7 +3508,7 @@
       <c r="F46" s="29"/>
     </row>
     <row r="47" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="36" t="s">
+      <c r="A47" s="34" t="s">
         <v>82</v>
       </c>
       <c r="B47" s="29"/>
@@ -3518,7 +3518,7 @@
       <c r="F47" s="29"/>
     </row>
     <row r="48" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="36" t="s">
+      <c r="A48" s="34" t="s">
         <v>83</v>
       </c>
       <c r="B48" s="29"/>
@@ -3528,7 +3528,7 @@
       <c r="F48" s="29"/>
     </row>
     <row r="49" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="36" t="s">
+      <c r="A49" s="34" t="s">
         <v>84</v>
       </c>
       <c r="B49" s="29"/>
@@ -3538,7 +3538,7 @@
       <c r="F49" s="29"/>
     </row>
     <row r="50" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="36" t="s">
+      <c r="A50" s="34" t="s">
         <v>85</v>
       </c>
       <c r="B50" s="29"/>
@@ -3548,7 +3548,7 @@
       <c r="F50" s="29"/>
     </row>
     <row r="51" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="36" t="s">
+      <c r="A51" s="34" t="s">
         <v>86</v>
       </c>
       <c r="B51" s="29"/>
@@ -3558,7 +3558,7 @@
       <c r="F51" s="29"/>
     </row>
     <row r="52" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="36" t="s">
+      <c r="A52" s="34" t="s">
         <v>87</v>
       </c>
       <c r="B52" s="29"/>
@@ -3569,14 +3569,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="B16:F16"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A52:F52"/>
@@ -3593,6 +3585,14 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B16:F16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3619,7 +3619,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="28" t="s">
         <v>88</v>
       </c>
       <c r="B1" s="29"/>
@@ -3634,7 +3634,7 @@
       <c r="K1" s="29"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>89</v>
       </c>
       <c r="B2" s="29"/>
@@ -3855,7 +3855,7 @@
         <v>116</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>106</v>
+        <v>724</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -3890,7 +3890,7 @@
         <v>120</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>106</v>
+        <v>724</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3925,7 +3925,7 @@
         <v>125</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>106</v>
+        <v>724</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -5819,15 +5819,15 @@
       </c>
     </row>
     <row r="65" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="31" t="s">
+      <c r="A65" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="B65" s="32"/>
-      <c r="C65" s="32"/>
-      <c r="D65" s="32"/>
-      <c r="E65" s="32"/>
-      <c r="F65" s="32"/>
-      <c r="G65" s="32"/>
+      <c r="B65" s="33"/>
+      <c r="C65" s="33"/>
+      <c r="D65" s="33"/>
+      <c r="E65" s="33"/>
+      <c r="F65" s="33"/>
+      <c r="G65" s="33"/>
       <c r="H65" s="21">
         <f>SUM(H4:H64)</f>
         <v>126</v>
@@ -5840,7 +5840,7 @@
       <c r="K65" s="20"/>
     </row>
     <row r="67" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="28" t="s">
+      <c r="A67" s="30" t="s">
         <v>379</v>
       </c>
       <c r="B67" s="29"/>
@@ -5855,7 +5855,7 @@
       <c r="K67" s="29"/>
     </row>
     <row r="68" spans="1:11" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="28" t="s">
+      <c r="A68" s="30" t="s">
         <v>380</v>
       </c>
       <c r="B68" s="29"/>
@@ -5870,7 +5870,7 @@
       <c r="K68" s="29"/>
     </row>
     <row r="69" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="28" t="s">
+      <c r="A69" s="30" t="s">
         <v>381</v>
       </c>
       <c r="B69" s="29"/>
@@ -5885,7 +5885,7 @@
       <c r="K69" s="29"/>
     </row>
     <row r="70" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="28" t="s">
+      <c r="A70" s="30" t="s">
         <v>382</v>
       </c>
       <c r="B70" s="29"/>
@@ -5956,7 +5956,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="28" t="s">
         <v>383</v>
       </c>
       <c r="B1" s="29"/>
@@ -5966,7 +5966,7 @@
       <c r="F1" s="29"/>
     </row>
     <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>384</v>
       </c>
       <c r="B2" s="29"/>
@@ -6582,7 +6582,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="28" t="s">
         <v>481</v>
       </c>
       <c r="B1" s="29"/>
@@ -6593,7 +6593,7 @@
       <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>482</v>
       </c>
       <c r="B2" s="29"/>
@@ -7320,7 +7320,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="28" t="s">
         <v>565</v>
       </c>
       <c r="B1" s="29"/>
@@ -7331,7 +7331,7 @@
       <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>566</v>
       </c>
       <c r="B2" s="29"/>
@@ -7699,7 +7699,7 @@
       <c r="G17" s="9"/>
     </row>
     <row r="19" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="34" t="s">
         <v>618</v>
       </c>
       <c r="B19" s="29"/>
@@ -7710,7 +7710,7 @@
       <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="34" t="s">
         <v>619</v>
       </c>
       <c r="B20" s="29"/>
@@ -7721,7 +7721,7 @@
       <c r="G20" s="29"/>
     </row>
     <row r="21" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="34" t="s">
         <v>620</v>
       </c>
       <c r="B21" s="29"/>
@@ -7758,7 +7758,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="28" t="s">
         <v>621</v>
       </c>
       <c r="B1" s="29"/>
@@ -7767,7 +7767,7 @@
       <c r="E1" s="29"/>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>622</v>
       </c>
       <c r="B2" s="29"/>
@@ -8035,7 +8035,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="28" t="s">
         <v>664</v>
       </c>
       <c r="B1" s="29"/>
@@ -8046,7 +8046,7 @@
       <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>665</v>
       </c>
       <c r="B2" s="29"/>

--- a/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
+++ b/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekin\Desktop\FDN\kalori\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB54609-98C3-41C5-908F-6886EA15291E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A4D099-20F2-46B7-8E2B-90690C7CDEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ozet Dashboard" sheetId="1" r:id="rId1"/>
@@ -2474,13 +2474,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2922,181 +2922,181 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
     </row>
     <row r="7" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
     </row>
     <row r="8" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
     </row>
     <row r="9" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
     </row>
     <row r="10" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
     </row>
     <row r="11" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
     </row>
     <row r="12" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
     </row>
     <row r="13" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
     </row>
     <row r="14" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
     </row>
     <row r="15" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
     </row>
     <row r="16" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
     </row>
     <row r="17" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
     </row>
     <row r="18" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
     </row>
     <row r="19" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -3137,11 +3137,11 @@
       </c>
       <c r="D23" s="6">
         <f>SUMIFS('Sprint Plani'!$H$4:$H$64,'Sprint Plani'!$A$4:$A$64,$A23,'Sprint Plani'!$K$4:$K$64,"Tamamlandı")</f>
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="E23" s="7">
         <f>IFERROR($D23/$C23,0)</f>
-        <v>0.45833333333333331</v>
+        <v>0.75</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>41</v>
@@ -3209,11 +3209,11 @@
       </c>
       <c r="D26" s="10">
         <f>SUM(D23:D25)</f>
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="E26" s="11">
         <f>IFERROR(D26/C26,0)</f>
-        <v>0.13095238095238096</v>
+        <v>0.21428571428571427</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>47</v>
@@ -3498,7 +3498,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="34" t="s">
+      <c r="A46" s="36" t="s">
         <v>81</v>
       </c>
       <c r="B46" s="29"/>
@@ -3508,7 +3508,7 @@
       <c r="F46" s="29"/>
     </row>
     <row r="47" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="34" t="s">
+      <c r="A47" s="36" t="s">
         <v>82</v>
       </c>
       <c r="B47" s="29"/>
@@ -3518,7 +3518,7 @@
       <c r="F47" s="29"/>
     </row>
     <row r="48" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="34" t="s">
+      <c r="A48" s="36" t="s">
         <v>83</v>
       </c>
       <c r="B48" s="29"/>
@@ -3528,7 +3528,7 @@
       <c r="F48" s="29"/>
     </row>
     <row r="49" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="34" t="s">
+      <c r="A49" s="36" t="s">
         <v>84</v>
       </c>
       <c r="B49" s="29"/>
@@ -3538,7 +3538,7 @@
       <c r="F49" s="29"/>
     </row>
     <row r="50" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="34" t="s">
+      <c r="A50" s="36" t="s">
         <v>85</v>
       </c>
       <c r="B50" s="29"/>
@@ -3548,7 +3548,7 @@
       <c r="F50" s="29"/>
     </row>
     <row r="51" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="34" t="s">
+      <c r="A51" s="36" t="s">
         <v>86</v>
       </c>
       <c r="B51" s="29"/>
@@ -3558,7 +3558,7 @@
       <c r="F51" s="29"/>
     </row>
     <row r="52" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="34" t="s">
+      <c r="A52" s="36" t="s">
         <v>87</v>
       </c>
       <c r="B52" s="29"/>
@@ -3569,6 +3569,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A52:F52"/>
@@ -3585,14 +3593,6 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="B16:F16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3960,7 +3960,7 @@
         <v>111</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>106</v>
+        <v>724</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -3995,7 +3995,7 @@
         <v>125</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>106</v>
+        <v>724</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -4030,7 +4030,7 @@
         <v>137</v>
       </c>
       <c r="K13" s="18" t="s">
-        <v>106</v>
+        <v>724</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4065,7 +4065,7 @@
         <v>105</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>106</v>
+        <v>724</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -4100,7 +4100,7 @@
         <v>99</v>
       </c>
       <c r="K15" s="18" t="s">
-        <v>106</v>
+        <v>724</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -7699,7 +7699,7 @@
       <c r="G17" s="9"/>
     </row>
     <row r="19" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="34" t="s">
+      <c r="A19" s="36" t="s">
         <v>618</v>
       </c>
       <c r="B19" s="29"/>
@@ -7710,7 +7710,7 @@
       <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="34" t="s">
+      <c r="A20" s="36" t="s">
         <v>619</v>
       </c>
       <c r="B20" s="29"/>
@@ -7721,7 +7721,7 @@
       <c r="G20" s="29"/>
     </row>
     <row r="21" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="36" t="s">
         <v>620</v>
       </c>
       <c r="B21" s="29"/>

--- a/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
+++ b/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekin\Desktop\FDN\kalori\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A4D099-20F2-46B7-8E2B-90690C7CDEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3109C570-949F-4F2F-BF88-140E86E3D8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ozet Dashboard" sheetId="1" r:id="rId1"/>
@@ -2474,13 +2474,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2922,181 +2922,181 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
     </row>
     <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
     </row>
     <row r="7" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
     </row>
     <row r="8" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
     </row>
     <row r="10" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
     </row>
     <row r="11" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
     </row>
     <row r="12" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
     </row>
     <row r="13" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
     </row>
     <row r="14" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
     </row>
     <row r="15" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
     </row>
     <row r="16" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
     </row>
     <row r="17" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
     </row>
     <row r="18" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
     </row>
     <row r="19" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -3137,11 +3137,11 @@
       </c>
       <c r="D23" s="6">
         <f>SUMIFS('Sprint Plani'!$H$4:$H$64,'Sprint Plani'!$A$4:$A$64,$A23,'Sprint Plani'!$K$4:$K$64,"Tamamlandı")</f>
-        <v>27</v>
+        <v>32.5</v>
       </c>
       <c r="E23" s="7">
         <f>IFERROR($D23/$C23,0)</f>
-        <v>0.75</v>
+        <v>0.90277777777777779</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>41</v>
@@ -3209,11 +3209,11 @@
       </c>
       <c r="D26" s="10">
         <f>SUM(D23:D25)</f>
-        <v>27</v>
+        <v>32.5</v>
       </c>
       <c r="E26" s="11">
         <f>IFERROR(D26/C26,0)</f>
-        <v>0.21428571428571427</v>
+        <v>0.25793650793650796</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>47</v>
@@ -3498,7 +3498,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="34" t="s">
         <v>81</v>
       </c>
       <c r="B46" s="29"/>
@@ -3508,7 +3508,7 @@
       <c r="F46" s="29"/>
     </row>
     <row r="47" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="36" t="s">
+      <c r="A47" s="34" t="s">
         <v>82</v>
       </c>
       <c r="B47" s="29"/>
@@ -3518,7 +3518,7 @@
       <c r="F47" s="29"/>
     </row>
     <row r="48" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="36" t="s">
+      <c r="A48" s="34" t="s">
         <v>83</v>
       </c>
       <c r="B48" s="29"/>
@@ -3528,7 +3528,7 @@
       <c r="F48" s="29"/>
     </row>
     <row r="49" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="36" t="s">
+      <c r="A49" s="34" t="s">
         <v>84</v>
       </c>
       <c r="B49" s="29"/>
@@ -3538,7 +3538,7 @@
       <c r="F49" s="29"/>
     </row>
     <row r="50" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="36" t="s">
+      <c r="A50" s="34" t="s">
         <v>85</v>
       </c>
       <c r="B50" s="29"/>
@@ -3548,7 +3548,7 @@
       <c r="F50" s="29"/>
     </row>
     <row r="51" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="36" t="s">
+      <c r="A51" s="34" t="s">
         <v>86</v>
       </c>
       <c r="B51" s="29"/>
@@ -3558,7 +3558,7 @@
       <c r="F51" s="29"/>
     </row>
     <row r="52" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="36" t="s">
+      <c r="A52" s="34" t="s">
         <v>87</v>
       </c>
       <c r="B52" s="29"/>
@@ -3569,14 +3569,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="B16:F16"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A52:F52"/>
@@ -3593,6 +3585,14 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B16:F16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4135,7 +4135,7 @@
         <v>105</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>106</v>
+        <v>724</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -4170,7 +4170,7 @@
         <v>156</v>
       </c>
       <c r="K17" s="18" t="s">
-        <v>106</v>
+        <v>724</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4205,7 +4205,7 @@
         <v>156</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>106</v>
+        <v>724</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -7699,7 +7699,7 @@
       <c r="G17" s="9"/>
     </row>
     <row r="19" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="34" t="s">
         <v>618</v>
       </c>
       <c r="B19" s="29"/>
@@ -7710,7 +7710,7 @@
       <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="34" t="s">
         <v>619</v>
       </c>
       <c r="B20" s="29"/>
@@ -7721,7 +7721,7 @@
       <c r="G20" s="29"/>
     </row>
     <row r="21" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="34" t="s">
         <v>620</v>
       </c>
       <c r="B21" s="29"/>

--- a/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
+++ b/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekin\Desktop\FDN\kalori\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3109C570-949F-4F2F-BF88-140E86E3D8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34CD7E68-5065-4A11-A3A9-D59F6E0F8081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DB ve Backend Degisiklikleri'!$A$3:$G$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Risk Yonetimi'!$A$3:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sprint Plani'!$A$3:$K$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sprint Plani'!$A$3:$K$65</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="732">
   <si>
     <t>OZET DASHBOARD  |  Kalan 14 Is Gunu</t>
   </si>
@@ -934,15 +934,6 @@
     <t>W4-T04</t>
   </si>
   <si>
-    <t>Öğrenen Profil Geri Besleme Döngüsü</t>
-  </si>
-  <si>
-    <t>recipe_feedback olaylari user_taste_weights tablosunu ustel hareketli ortalama ile gunceller. Boyutlar: cuisine, diet_tag, ingredient, difficulty, sure_araligi. 'sevmedim' -&gt; negatif agirlik, 'yapacagim'/'yaptim' -&gt; pozitif, 'cok_uzun' -&gt; sure boyutunda negatif. KURAL: ogrenilen tercih, beyan edilen diyet/alerjen kisitini ASLA ezemez.</t>
-  </si>
-  <si>
-    <t>10 swipe sonrasi oneri sirasi olculebilir sekilde degisiyor; alerjen filtresi hic etkilenmiyor.</t>
-  </si>
-  <si>
     <t>W4-T05</t>
   </si>
   <si>
@@ -2243,6 +2234,36 @@
   </si>
   <si>
     <t>Tamamlandı</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>W3-T02B</t>
+  </si>
+  <si>
+    <t>Backend / Onboarding+Algoritma</t>
+  </si>
+  <si>
+    <t>Onboarding Ucu ve Zevk Öğrenme Motoru</t>
+  </si>
+  <si>
+    <t>POST /onboarding ucu yazılır: profile→user_profiles (Mifflin-St Jeor ile BMR/TDEE/makro hesabı, eksik alanlarda varsayılan 2000 kcal), diet_tag_codes/allergen_codes→user_diet_tags/user_allergens, liked_recipe_ids→recipe_feedback(begendim). UserTasteWeight için örneklem-ortalaması güncelleme motoru yazılır: weight += (sinyal - weight)/event_count, boyutlar cuisine/diet_tag/ingredient/difficulty. Aynı motor swipe_service.record_swipe'a da bağlanır (begendim/begenmedim-sevmedim/yaptim öğrenen sinyal üretir; gordu/malzeme_yok/cok_uzun kural tabanlı kalır, dokunmaz).</t>
+  </si>
+  <si>
+    <t>Onboarding tamamlanınca 4 tabloya + user_taste_weights'e kayıt gidiyor; 'Atla' ile 2000 kcal varsayılanı çalışıyor; kural tabanlı skorlama (T06) hiç kullanıcı verisi olmadan ilk günden çalışıyor; kullanıcı başına ~20-50 swipe sonrası öneri sırası ölçülebilir şekilde değişiyor.</t>
+  </si>
+  <si>
+    <t>Öğrenen Profil Motorunun Gerçek Veriyle Doğrulanması</t>
+  </si>
+  <si>
+    <t>W3-T02B'de kurulan UserTasteWeight motoru gerçek swipe verisiyle sınanır: event_count dağılımı ve ağırlık yakınsaması loglanır; gerekirse sinyal güçleri (begendim=1, yaptim=3 kat, sevmedim=-1) ayarlanır; T06'nın zevk bileşeni açık/kapalı iki durumda öneri sırası karşılaştırılır.</t>
+  </si>
+  <si>
+    <t>En az 20-30 swipe yapmış test kullanıcısında öneri sıralaması ölçülebilir şekilde değişiyor; bulgular docs/ altına yazıldı.</t>
+  </si>
+  <si>
+    <t>W3-T02B, W3-T09</t>
   </si>
 </sst>
 </file>
@@ -2381,7 +2402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2474,13 +2495,25 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2922,181 +2955,181 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
     </row>
     <row r="7" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
     </row>
     <row r="8" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
     </row>
     <row r="9" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
     </row>
     <row r="10" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
     </row>
     <row r="11" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
     </row>
     <row r="12" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
     </row>
     <row r="13" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
     </row>
     <row r="14" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
     </row>
     <row r="15" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
     </row>
     <row r="16" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
     </row>
     <row r="17" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
     </row>
     <row r="18" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
     </row>
     <row r="19" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -3128,20 +3161,20 @@
         <v>40</v>
       </c>
       <c r="B23" s="5">
-        <f>COUNTIF('Sprint Plani'!$A$4:$A$64,$A23)</f>
+        <f>COUNTIF('Sprint Plani'!$A$4:$A$65,$A23)</f>
         <v>17</v>
       </c>
       <c r="C23" s="6">
-        <f>SUMIF('Sprint Plani'!$A$4:$A$64,$A23,'Sprint Plani'!$H$4:$H$64)</f>
+        <f>SUMIF('Sprint Plani'!$A$4:$A$65,$A23,'Sprint Plani'!$H$4:$H$65)</f>
         <v>36</v>
       </c>
       <c r="D23" s="6">
-        <f>SUMIFS('Sprint Plani'!$H$4:$H$64,'Sprint Plani'!$A$4:$A$64,$A23,'Sprint Plani'!$K$4:$K$64,"Tamamlandı")</f>
-        <v>32.5</v>
+        <f>SUMIFS('Sprint Plani'!$H$4:$H$65,'Sprint Plani'!$A$4:$A$65,$A23,'Sprint Plani'!$K$4:$K$65,"Tamamlandı")</f>
+        <v>36</v>
       </c>
       <c r="E23" s="7">
         <f>IFERROR($D23/$C23,0)</f>
-        <v>0.90277777777777779</v>
+        <v>1</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>41</v>
@@ -3152,20 +3185,20 @@
         <v>42</v>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF('Sprint Plani'!$A$4:$A$64,$A24)</f>
-        <v>21</v>
+        <f>COUNTIF('Sprint Plani'!$A$4:$A$65,$A24)</f>
+        <v>22</v>
       </c>
       <c r="C24" s="6">
-        <f>SUMIF('Sprint Plani'!$A$4:$A$64,$A24,'Sprint Plani'!$H$4:$H$64)</f>
-        <v>45</v>
+        <f>SUMIF('Sprint Plani'!$A$4:$A$65,$A24,'Sprint Plani'!$H$4:$H$65)</f>
+        <v>49</v>
       </c>
       <c r="D24" s="6">
-        <f>SUMIFS('Sprint Plani'!$H$4:$H$64,'Sprint Plani'!$A$4:$A$64,$A24,'Sprint Plani'!$K$4:$K$64,"Tamamlandı")</f>
-        <v>0</v>
+        <f>SUMIFS('Sprint Plani'!$H$4:$H$65,'Sprint Plani'!$A$4:$A$65,$A24,'Sprint Plani'!$K$4:$K$65,"Tamamlandı")</f>
+        <v>7.5</v>
       </c>
       <c r="E24" s="7">
         <f>IFERROR($D24/$C24,0)</f>
-        <v>0</v>
+        <v>0.15306122448979592</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>43</v>
@@ -3176,15 +3209,15 @@
         <v>44</v>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF('Sprint Plani'!$A$4:$A$64,$A25)</f>
+        <f>COUNTIF('Sprint Plani'!$A$4:$A$65,$A25)</f>
         <v>23</v>
       </c>
       <c r="C25" s="6">
-        <f>SUMIF('Sprint Plani'!$A$4:$A$64,$A25,'Sprint Plani'!$H$4:$H$64)</f>
-        <v>45</v>
+        <f>SUMIF('Sprint Plani'!$A$4:$A$65,$A25,'Sprint Plani'!$H$4:$H$65)</f>
+        <v>44.5</v>
       </c>
       <c r="D25" s="6">
-        <f>SUMIFS('Sprint Plani'!$H$4:$H$64,'Sprint Plani'!$A$4:$A$64,$A25,'Sprint Plani'!$K$4:$K$64,"Tamamlandı")</f>
+        <f>SUMIFS('Sprint Plani'!$H$4:$H$65,'Sprint Plani'!$A$4:$A$65,$A25,'Sprint Plani'!$K$4:$K$65,"Tamamlandı")</f>
         <v>0</v>
       </c>
       <c r="E25" s="7">
@@ -3201,19 +3234,19 @@
       </c>
       <c r="B26" s="9">
         <f>SUM(B23:B25)</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="10">
         <f>SUM(C23:C25)</f>
-        <v>126</v>
+        <v>129.5</v>
       </c>
       <c r="D26" s="10">
         <f>SUM(D23:D25)</f>
-        <v>32.5</v>
+        <v>43.5</v>
       </c>
       <c r="E26" s="11">
         <f>IFERROR(D26/C26,0)</f>
-        <v>0.25793650793650796</v>
+        <v>0.3359073359073359</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>47</v>
@@ -3245,11 +3278,11 @@
         <v>52</v>
       </c>
       <c r="B30" s="14">
-        <f>COUNTIF('Sprint Plani'!$B$4:$B$64,$A30)</f>
+        <f>COUNTIF('Sprint Plani'!$B$4:$B$65,$A30)</f>
         <v>4</v>
       </c>
       <c r="C30" s="15">
-        <f>SUMIF('Sprint Plani'!$B$4:$B$64,$A30,'Sprint Plani'!$H$4:$H$64)</f>
+        <f>SUMIF('Sprint Plani'!$B$4:$B$65,$A30,'Sprint Plani'!$H$4:$H$65)</f>
         <v>9</v>
       </c>
       <c r="D30" s="14"/>
@@ -3263,11 +3296,11 @@
         <v>54</v>
       </c>
       <c r="B31" s="14">
-        <f>COUNTIF('Sprint Plani'!$B$4:$B$64,$A31)</f>
+        <f>COUNTIF('Sprint Plani'!$B$4:$B$65,$A31)</f>
         <v>4</v>
       </c>
       <c r="C31" s="15">
-        <f>SUMIF('Sprint Plani'!$B$4:$B$64,$A31,'Sprint Plani'!$H$4:$H$64)</f>
+        <f>SUMIF('Sprint Plani'!$B$4:$B$65,$A31,'Sprint Plani'!$H$4:$H$65)</f>
         <v>9</v>
       </c>
       <c r="D31" s="14"/>
@@ -3281,11 +3314,11 @@
         <v>56</v>
       </c>
       <c r="B32" s="14">
-        <f>COUNTIF('Sprint Plani'!$B$4:$B$64,$A32)</f>
+        <f>COUNTIF('Sprint Plani'!$B$4:$B$65,$A32)</f>
         <v>4</v>
       </c>
       <c r="C32" s="15">
-        <f>SUMIF('Sprint Plani'!$B$4:$B$64,$A32,'Sprint Plani'!$H$4:$H$64)</f>
+        <f>SUMIF('Sprint Plani'!$B$4:$B$65,$A32,'Sprint Plani'!$H$4:$H$65)</f>
         <v>9</v>
       </c>
       <c r="D32" s="14"/>
@@ -3299,11 +3332,11 @@
         <v>58</v>
       </c>
       <c r="B33" s="14">
-        <f>COUNTIF('Sprint Plani'!$B$4:$B$64,$A33)</f>
+        <f>COUNTIF('Sprint Plani'!$B$4:$B$65,$A33)</f>
         <v>5</v>
       </c>
       <c r="C33" s="15">
-        <f>SUMIF('Sprint Plani'!$B$4:$B$64,$A33,'Sprint Plani'!$H$4:$H$64)</f>
+        <f>SUMIF('Sprint Plani'!$B$4:$B$65,$A33,'Sprint Plani'!$H$4:$H$65)</f>
         <v>9</v>
       </c>
       <c r="D33" s="14"/>
@@ -3317,12 +3350,12 @@
         <v>60</v>
       </c>
       <c r="B34" s="14">
-        <f>COUNTIF('Sprint Plani'!$B$4:$B$64,$A34)</f>
-        <v>5</v>
+        <f>COUNTIF('Sprint Plani'!$B$4:$B$65,$A34)</f>
+        <v>6</v>
       </c>
       <c r="C34" s="15">
-        <f>SUMIF('Sprint Plani'!$B$4:$B$64,$A34,'Sprint Plani'!$H$4:$H$64)</f>
-        <v>9</v>
+        <f>SUMIF('Sprint Plani'!$B$4:$B$65,$A34,'Sprint Plani'!$H$4:$H$65)</f>
+        <v>13</v>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
@@ -3335,11 +3368,11 @@
         <v>62</v>
       </c>
       <c r="B35" s="14">
-        <f>COUNTIF('Sprint Plani'!$B$4:$B$64,$A35)</f>
+        <f>COUNTIF('Sprint Plani'!$B$4:$B$65,$A35)</f>
         <v>4</v>
       </c>
       <c r="C35" s="15">
-        <f>SUMIF('Sprint Plani'!$B$4:$B$64,$A35,'Sprint Plani'!$H$4:$H$64)</f>
+        <f>SUMIF('Sprint Plani'!$B$4:$B$65,$A35,'Sprint Plani'!$H$4:$H$65)</f>
         <v>9</v>
       </c>
       <c r="D35" s="14"/>
@@ -3353,11 +3386,11 @@
         <v>64</v>
       </c>
       <c r="B36" s="14">
-        <f>COUNTIF('Sprint Plani'!$B$4:$B$64,$A36)</f>
+        <f>COUNTIF('Sprint Plani'!$B$4:$B$65,$A36)</f>
         <v>4</v>
       </c>
       <c r="C36" s="15">
-        <f>SUMIF('Sprint Plani'!$B$4:$B$64,$A36,'Sprint Plani'!$H$4:$H$64)</f>
+        <f>SUMIF('Sprint Plani'!$B$4:$B$65,$A36,'Sprint Plani'!$H$4:$H$65)</f>
         <v>9</v>
       </c>
       <c r="D36" s="14"/>
@@ -3371,11 +3404,11 @@
         <v>66</v>
       </c>
       <c r="B37" s="14">
-        <f>COUNTIF('Sprint Plani'!$B$4:$B$64,$A37)</f>
+        <f>COUNTIF('Sprint Plani'!$B$4:$B$65,$A37)</f>
         <v>4</v>
       </c>
       <c r="C37" s="15">
-        <f>SUMIF('Sprint Plani'!$B$4:$B$64,$A37,'Sprint Plani'!$H$4:$H$64)</f>
+        <f>SUMIF('Sprint Plani'!$B$4:$B$65,$A37,'Sprint Plani'!$H$4:$H$65)</f>
         <v>9</v>
       </c>
       <c r="D37" s="14"/>
@@ -3389,11 +3422,11 @@
         <v>68</v>
       </c>
       <c r="B38" s="14">
-        <f>COUNTIF('Sprint Plani'!$B$4:$B$64,$A38)</f>
+        <f>COUNTIF('Sprint Plani'!$B$4:$B$65,$A38)</f>
         <v>4</v>
       </c>
       <c r="C38" s="15">
-        <f>SUMIF('Sprint Plani'!$B$4:$B$64,$A38,'Sprint Plani'!$H$4:$H$64)</f>
+        <f>SUMIF('Sprint Plani'!$B$4:$B$65,$A38,'Sprint Plani'!$H$4:$H$65)</f>
         <v>9</v>
       </c>
       <c r="D38" s="14"/>
@@ -3407,12 +3440,12 @@
         <v>70</v>
       </c>
       <c r="B39" s="14">
-        <f>COUNTIF('Sprint Plani'!$B$4:$B$64,$A39)</f>
+        <f>COUNTIF('Sprint Plani'!$B$4:$B$65,$A39)</f>
         <v>4</v>
       </c>
       <c r="C39" s="15">
-        <f>SUMIF('Sprint Plani'!$B$4:$B$64,$A39,'Sprint Plani'!$H$4:$H$64)</f>
-        <v>9</v>
+        <f>SUMIF('Sprint Plani'!$B$4:$B$65,$A39,'Sprint Plani'!$H$4:$H$65)</f>
+        <v>8.5</v>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
@@ -3425,11 +3458,11 @@
         <v>72</v>
       </c>
       <c r="B40" s="14">
-        <f>COUNTIF('Sprint Plani'!$B$4:$B$64,$A40)</f>
+        <f>COUNTIF('Sprint Plani'!$B$4:$B$65,$A40)</f>
         <v>5</v>
       </c>
       <c r="C40" s="15">
-        <f>SUMIF('Sprint Plani'!$B$4:$B$64,$A40,'Sprint Plani'!$H$4:$H$64)</f>
+        <f>SUMIF('Sprint Plani'!$B$4:$B$65,$A40,'Sprint Plani'!$H$4:$H$65)</f>
         <v>9</v>
       </c>
       <c r="D40" s="14"/>
@@ -3443,11 +3476,11 @@
         <v>74</v>
       </c>
       <c r="B41" s="14">
-        <f>COUNTIF('Sprint Plani'!$B$4:$B$64,$A41)</f>
+        <f>COUNTIF('Sprint Plani'!$B$4:$B$65,$A41)</f>
         <v>4</v>
       </c>
       <c r="C41" s="15">
-        <f>SUMIF('Sprint Plani'!$B$4:$B$64,$A41,'Sprint Plani'!$H$4:$H$64)</f>
+        <f>SUMIF('Sprint Plani'!$B$4:$B$65,$A41,'Sprint Plani'!$H$4:$H$65)</f>
         <v>9</v>
       </c>
       <c r="D41" s="14"/>
@@ -3461,11 +3494,11 @@
         <v>76</v>
       </c>
       <c r="B42" s="14">
-        <f>COUNTIF('Sprint Plani'!$B$4:$B$64,$A42)</f>
+        <f>COUNTIF('Sprint Plani'!$B$4:$B$65,$A42)</f>
         <v>5</v>
       </c>
       <c r="C42" s="15">
-        <f>SUMIF('Sprint Plani'!$B$4:$B$64,$A42,'Sprint Plani'!$H$4:$H$64)</f>
+        <f>SUMIF('Sprint Plani'!$B$4:$B$65,$A42,'Sprint Plani'!$H$4:$H$65)</f>
         <v>9</v>
       </c>
       <c r="D42" s="14"/>
@@ -3479,11 +3512,11 @@
         <v>78</v>
       </c>
       <c r="B43" s="14">
-        <f>COUNTIF('Sprint Plani'!$B$4:$B$64,$A43)</f>
+        <f>COUNTIF('Sprint Plani'!$B$4:$B$65,$A43)</f>
         <v>5</v>
       </c>
       <c r="C43" s="15">
-        <f>SUMIF('Sprint Plani'!$B$4:$B$64,$A43,'Sprint Plani'!$H$4:$H$64)</f>
+        <f>SUMIF('Sprint Plani'!$B$4:$B$65,$A43,'Sprint Plani'!$H$4:$H$65)</f>
         <v>9</v>
       </c>
       <c r="D43" s="14"/>
@@ -3498,7 +3531,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="34" t="s">
+      <c r="A46" s="36" t="s">
         <v>81</v>
       </c>
       <c r="B46" s="29"/>
@@ -3508,7 +3541,7 @@
       <c r="F46" s="29"/>
     </row>
     <row r="47" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="34" t="s">
+      <c r="A47" s="36" t="s">
         <v>82</v>
       </c>
       <c r="B47" s="29"/>
@@ -3518,7 +3551,7 @@
       <c r="F47" s="29"/>
     </row>
     <row r="48" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="34" t="s">
+      <c r="A48" s="36" t="s">
         <v>83</v>
       </c>
       <c r="B48" s="29"/>
@@ -3528,7 +3561,7 @@
       <c r="F48" s="29"/>
     </row>
     <row r="49" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="34" t="s">
+      <c r="A49" s="36" t="s">
         <v>84</v>
       </c>
       <c r="B49" s="29"/>
@@ -3538,7 +3571,7 @@
       <c r="F49" s="29"/>
     </row>
     <row r="50" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="34" t="s">
+      <c r="A50" s="36" t="s">
         <v>85</v>
       </c>
       <c r="B50" s="29"/>
@@ -3548,7 +3581,7 @@
       <c r="F50" s="29"/>
     </row>
     <row r="51" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="34" t="s">
+      <c r="A51" s="36" t="s">
         <v>86</v>
       </c>
       <c r="B51" s="29"/>
@@ -3558,7 +3591,7 @@
       <c r="F51" s="29"/>
     </row>
     <row r="52" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="34" t="s">
+      <c r="A52" s="36" t="s">
         <v>87</v>
       </c>
       <c r="B52" s="29"/>
@@ -3569,6 +3602,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A52:F52"/>
@@ -3585,14 +3626,6 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="B16:F16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3603,7 +3636,7 @@
   <sheetPr>
     <tabColor rgb="FF2E75B6"/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9" customWidth="1"/>
@@ -3650,7 +3683,7 @@
     </row>
     <row r="3" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>722</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>49</v>
@@ -3715,7 +3748,7 @@
         <v>105</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -3750,7 +3783,7 @@
         <v>99</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -3785,7 +3818,7 @@
         <v>105</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -3820,7 +3853,7 @@
         <v>111</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -3855,7 +3888,7 @@
         <v>116</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -3890,7 +3923,7 @@
         <v>120</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3925,7 +3958,7 @@
         <v>125</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -3960,7 +3993,7 @@
         <v>111</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -3995,7 +4028,7 @@
         <v>125</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -4030,7 +4063,7 @@
         <v>137</v>
       </c>
       <c r="K13" s="18" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4065,7 +4098,7 @@
         <v>105</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -4100,7 +4133,7 @@
         <v>99</v>
       </c>
       <c r="K15" s="18" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -4135,7 +4168,7 @@
         <v>105</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -4170,7 +4203,7 @@
         <v>156</v>
       </c>
       <c r="K17" s="18" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4205,7 +4238,7 @@
         <v>156</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4240,7 +4273,7 @@
         <v>156</v>
       </c>
       <c r="K19" s="18" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4275,7 +4308,7 @@
         <v>171</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
@@ -4310,7 +4343,7 @@
         <v>171</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
@@ -4345,33 +4378,33 @@
         <v>181</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" s="38" customFormat="1" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>194</v>
+      <c r="C23" s="37" t="s">
+        <v>723</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>724</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>725</v>
+      </c>
+      <c r="F23" s="40" t="s">
+        <v>726</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>727</v>
       </c>
       <c r="H23" s="18">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I23" s="18" t="s">
         <v>104</v>
@@ -4380,1483 +4413,1503 @@
         <v>186</v>
       </c>
       <c r="K23" s="18" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="H24" s="18">
+        <v>3.5</v>
+      </c>
+      <c r="I24" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="J24" s="18" t="s">
+        <v>723</v>
+      </c>
+      <c r="K24" s="18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" t="s">
+    <row r="25" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B25" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C25" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D25" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E25" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F25" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="G24" s="17" t="s">
+      <c r="G25" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H25" s="16">
         <v>1</v>
       </c>
-      <c r="I24" s="16" t="s">
+      <c r="I25" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="J24" s="16" t="s">
+      <c r="J25" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="K24" s="16" t="s">
+      <c r="K25" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
+    <row r="26" spans="1:11" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C26" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D26" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E26" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="F25" s="19" t="s">
+      <c r="F26" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="G26" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="H25" s="18">
+      <c r="H26" s="18">
         <v>1</v>
       </c>
-      <c r="I25" s="18" t="s">
+      <c r="I26" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="J25" s="18" t="s">
+      <c r="J26" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="K25" s="18" t="s">
+      <c r="K26" s="18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="16" t="s">
+    <row r="27" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B27" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C27" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D27" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E27" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="F27" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="G26" s="17" t="s">
+      <c r="G27" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H27" s="16">
         <v>3</v>
       </c>
-      <c r="I26" s="16" t="s">
+      <c r="I27" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="J26" s="16" t="s">
+      <c r="J27" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="K26" s="16" t="s">
+      <c r="K27" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="18" t="s">
+    <row r="28" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B28" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C28" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D28" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="E28" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="F28" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="G27" s="19" t="s">
+      <c r="G28" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="H27" s="18">
+      <c r="H28" s="18">
         <v>2</v>
       </c>
-      <c r="I27" s="18" t="s">
+      <c r="I28" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="J27" s="18" t="s">
+      <c r="J28" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="K27" s="18" t="s">
+      <c r="K28" s="18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="16" t="s">
+    <row r="29" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B29" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C29" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D29" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E29" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F29" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="G28" s="17" t="s">
+      <c r="G29" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="H28" s="16">
+      <c r="H29" s="16">
         <v>2</v>
       </c>
-      <c r="I28" s="16" t="s">
+      <c r="I29" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="J28" s="16" t="s">
+      <c r="J29" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="K28" s="16" t="s">
+      <c r="K29" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="18" t="s">
+    <row r="30" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B30" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C30" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D30" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E30" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="F30" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G30" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="H29" s="18">
+      <c r="H30" s="18">
         <v>2</v>
       </c>
-      <c r="I29" s="18" t="s">
+      <c r="I30" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="J29" s="18" t="s">
+      <c r="J30" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="K29" s="18" t="s">
+      <c r="K30" s="18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="16" t="s">
+    <row r="31" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B31" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C31" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D31" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E31" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="F30" s="17" t="s">
+      <c r="F31" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="G30" s="17" t="s">
+      <c r="G31" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="H30" s="16">
+      <c r="H31" s="16">
         <v>3</v>
       </c>
-      <c r="I30" s="16" t="s">
+      <c r="I31" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="J30" s="16" t="s">
+      <c r="J31" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="K30" s="16" t="s">
+      <c r="K31" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="18" t="s">
+    <row r="32" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B32" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C32" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D32" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="E32" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="F31" s="19" t="s">
+      <c r="F32" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="G31" s="19" t="s">
+      <c r="G32" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H31" s="18">
+      <c r="H32" s="18">
         <v>1.5</v>
       </c>
-      <c r="I31" s="18" t="s">
+      <c r="I32" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="J31" s="18" t="s">
+      <c r="J32" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="K31" s="18" t="s">
+      <c r="K32" s="18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="16" t="s">
+    <row r="33" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B33" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C33" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D33" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E33" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F33" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="G32" s="17" t="s">
+      <c r="G33" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H33" s="16">
         <v>2</v>
       </c>
-      <c r="I32" s="16" t="s">
+      <c r="I33" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="J32" s="16" t="s">
+      <c r="J33" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="K32" s="16" t="s">
+      <c r="K33" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="18" t="s">
+    <row r="34" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B34" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C34" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D34" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="E34" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="F33" s="19" t="s">
+      <c r="F34" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="G33" s="19" t="s">
+      <c r="G34" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="H33" s="18">
+      <c r="H34" s="18">
         <v>2.5</v>
       </c>
-      <c r="I33" s="18" t="s">
+      <c r="I34" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="J33" s="18" t="s">
+      <c r="J34" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="K33" s="18" t="s">
+      <c r="K34" s="18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="16" t="s">
+    <row r="35" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B35" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C35" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D35" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E35" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="F35" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="G34" s="17" t="s">
+      <c r="G35" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="H34" s="16">
+      <c r="H35" s="16">
         <v>3</v>
       </c>
-      <c r="I34" s="16" t="s">
+      <c r="I35" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="J34" s="16" t="s">
+      <c r="J35" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="K34" s="16" t="s">
+      <c r="K35" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="18" t="s">
+    <row r="36" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B36" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C36" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D36" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E36" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="F35" s="19" t="s">
+      <c r="F36" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="G35" s="19" t="s">
+      <c r="G36" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="H35" s="18">
+      <c r="H36" s="18">
         <v>3</v>
       </c>
-      <c r="I35" s="18" t="s">
+      <c r="I36" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="J35" s="18" t="s">
+      <c r="J36" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="K35" s="18" t="s">
+      <c r="K36" s="18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="16" t="s">
+    <row r="37" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B37" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C37" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D37" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E37" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="F36" s="17" t="s">
+      <c r="F37" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="G36" s="17" t="s">
+      <c r="G37" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="H36" s="16">
+      <c r="H37" s="16">
         <v>2</v>
       </c>
-      <c r="I36" s="16" t="s">
+      <c r="I37" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="J36" s="16" t="s">
+      <c r="J37" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="K36" s="16" t="s">
+      <c r="K37" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="18" t="s">
+    <row r="38" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="B38" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C38" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D38" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="E38" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="F37" s="19" t="s">
+      <c r="F38" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="G37" s="19" t="s">
+      <c r="G38" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="H37" s="18">
+      <c r="H38" s="18">
         <v>1</v>
       </c>
-      <c r="I37" s="18" t="s">
+      <c r="I38" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="J37" s="18" t="s">
+      <c r="J38" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="K37" s="18" t="s">
+      <c r="K38" s="18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="16" t="s">
+    <row r="39" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B39" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C39" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D39" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E39" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="F39" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="G38" s="17" t="s">
+      <c r="G39" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="H38" s="16">
+      <c r="H39" s="16">
         <v>2.5</v>
       </c>
-      <c r="I38" s="16" t="s">
+      <c r="I39" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="J38" s="16" t="s">
+      <c r="J39" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="K38" s="16" t="s">
+      <c r="K39" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="18" t="s">
+    <row r="40" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B40" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C40" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D40" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E40" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="F39" s="19" t="s">
+      <c r="F40" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="G39" s="19" t="s">
+      <c r="G40" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="H39" s="18">
+      <c r="H40" s="18">
         <v>3</v>
       </c>
-      <c r="I39" s="18" t="s">
+      <c r="I40" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="J39" s="18" t="s">
+      <c r="J40" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="K39" s="18" t="s">
+      <c r="K40" s="18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="16" t="s">
+    <row r="41" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B41" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C41" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D41" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E41" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="F40" s="17" t="s">
+      <c r="F41" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="G40" s="17" t="s">
+      <c r="G41" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="H40" s="16">
+      <c r="H41" s="16">
         <v>2</v>
       </c>
-      <c r="I40" s="16" t="s">
+      <c r="I41" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="J40" s="16" t="s">
+      <c r="J41" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="K40" s="16" t="s">
+      <c r="K41" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="18" t="s">
+    <row r="42" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="18" t="s">
+      <c r="B42" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C42" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D42" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="E41" s="19" t="s">
+      <c r="E42" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="F41" s="19" t="s">
+      <c r="F42" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="G41" s="19" t="s">
+      <c r="G42" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="H41" s="18">
+      <c r="H42" s="18">
         <v>1.5</v>
       </c>
-      <c r="I41" s="18" t="s">
+      <c r="I42" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="J41" s="18" t="s">
+      <c r="J42" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="K41" s="18" t="s">
+      <c r="K42" s="18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="16" t="s">
+    <row r="43" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B43" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C43" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D43" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E43" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="F43" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="G42" s="17" t="s">
+      <c r="G43" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="H42" s="16">
+      <c r="H43" s="16">
         <v>3</v>
       </c>
-      <c r="I42" s="16" t="s">
+      <c r="I43" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="J42" s="16" t="s">
+      <c r="J43" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="K42" s="16" t="s">
+      <c r="K43" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="18" t="s">
+    <row r="44" spans="1:11" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B43" s="18" t="s">
+      <c r="B44" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C44" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="D43" s="19" t="s">
+      <c r="D44" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="E43" s="19" t="s">
+      <c r="E44" s="19" t="s">
         <v>280</v>
       </c>
-      <c r="F43" s="19" t="s">
+      <c r="F44" s="19" t="s">
         <v>281</v>
       </c>
-      <c r="G43" s="19" t="s">
+      <c r="G44" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="H43" s="18">
+      <c r="H44" s="18">
         <v>1.5</v>
       </c>
-      <c r="I43" s="18" t="s">
+      <c r="I44" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="J43" s="18" t="s">
+      <c r="J44" s="18" t="s">
         <v>274</v>
       </c>
-      <c r="K43" s="18" t="s">
+      <c r="K44" s="18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="16" t="s">
+    <row r="45" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B45" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C45" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D45" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="E44" s="17" t="s">
+      <c r="E45" s="17" t="s">
         <v>284</v>
       </c>
-      <c r="F44" s="17" t="s">
+      <c r="F45" s="17" t="s">
         <v>285</v>
       </c>
-      <c r="G44" s="17" t="s">
+      <c r="G45" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="H44" s="16">
+      <c r="H45" s="16">
         <v>2.5</v>
       </c>
-      <c r="I44" s="16" t="s">
+      <c r="I45" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="J44" s="16" t="s">
+      <c r="J45" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="K44" s="16" t="s">
+      <c r="K45" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="18" t="s">
+    <row r="46" spans="1:11" s="38" customFormat="1" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="18" t="s">
+      <c r="B46" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C46" s="37" t="s">
         <v>287</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D46" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="E45" s="19" t="s">
+      <c r="E46" s="37" t="s">
+        <v>728</v>
+      </c>
+      <c r="F46" s="37" t="s">
+        <v>729</v>
+      </c>
+      <c r="G46" s="37" t="s">
+        <v>730</v>
+      </c>
+      <c r="H46" s="39">
+        <v>1.5</v>
+      </c>
+      <c r="I46" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="J46" s="37" t="s">
+        <v>731</v>
+      </c>
+      <c r="K46" s="37" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C47" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="F45" s="19" t="s">
+      <c r="D47" s="17" t="s">
         <v>289</v>
       </c>
-      <c r="G45" s="19" t="s">
+      <c r="E47" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="H45" s="18">
+      <c r="F47" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="G47" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="H47" s="16">
         <v>2</v>
       </c>
-      <c r="I45" s="18" t="s">
+      <c r="I47" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="J45" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="K45" s="18" t="s">
+      <c r="J47" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="K47" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="16" t="s">
+    <row r="48" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B48" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C46" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="D46" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="E46" s="17" t="s">
+      <c r="C48" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="F46" s="17" t="s">
+      <c r="D48" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="G46" s="17" t="s">
+      <c r="E48" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="H46" s="16">
+      <c r="F48" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="G48" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="H48" s="18">
         <v>2</v>
       </c>
-      <c r="I46" s="16" t="s">
+      <c r="I48" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="J48" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="K48" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="G49" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="H49" s="16">
+        <v>2</v>
+      </c>
+      <c r="I49" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="J49" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="D50" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="G50" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="H50" s="18">
+        <v>1.5</v>
+      </c>
+      <c r="I50" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="J50" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="K50" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="D51" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="G51" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="H51" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="I51" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="J51" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>311</v>
+      </c>
+      <c r="D52" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="G52" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="H52" s="18">
+        <v>3</v>
+      </c>
+      <c r="I52" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="J52" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="K52" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="F53" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="G53" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="H53" s="16">
+        <v>2</v>
+      </c>
+      <c r="I53" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="J53" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="G54" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="H54" s="18">
+        <v>2.5</v>
+      </c>
+      <c r="I54" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="J46" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="K46" s="16" t="s">
+      <c r="J54" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="K54" s="18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="18" t="s">
+    <row r="55" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B47" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C47" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="D47" s="19" t="s">
-        <v>297</v>
-      </c>
-      <c r="E47" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="F47" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="G47" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="H47" s="18">
+      <c r="B55" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="D55" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="G55" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="H55" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="I55" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="J55" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="D56" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="G56" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="H56" s="18">
+        <v>1.5</v>
+      </c>
+      <c r="I56" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="J56" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="K56" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="F57" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="G57" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="H57" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="I57" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="J57" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="F58" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="G58" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="H58" s="18">
         <v>2</v>
       </c>
-      <c r="I47" s="18" t="s">
+      <c r="I58" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="J47" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="K47" s="18" t="s">
+      <c r="J58" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="K58" s="18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="16" t="s">
+    <row r="59" spans="1:11" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="E48" s="17" t="s">
-        <v>302</v>
-      </c>
-      <c r="F48" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="G48" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="H48" s="16">
+      <c r="B59" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="D59" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="F59" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="G59" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="H59" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="I59" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="J59" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>349</v>
+      </c>
+      <c r="D60" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="E60" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="F60" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="G60" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="H60" s="18">
+        <v>1.5</v>
+      </c>
+      <c r="I60" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="J60" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="K60" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="D61" s="17" t="s">
+        <v>354</v>
+      </c>
+      <c r="E61" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="F61" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="G61" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="H61" s="16">
         <v>2</v>
       </c>
-      <c r="I48" s="16" t="s">
+      <c r="I61" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="J48" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="K48" s="16" t="s">
+      <c r="J61" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="K61" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="18" t="s">
+    <row r="62" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B49" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="D49" s="19" t="s">
-        <v>297</v>
-      </c>
-      <c r="E49" s="19" t="s">
-        <v>306</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>308</v>
-      </c>
-      <c r="H49" s="18">
-        <v>1.5</v>
-      </c>
-      <c r="I49" s="18" t="s">
+      <c r="B62" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="D62" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="E62" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="G62" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="H62" s="18">
+        <v>2</v>
+      </c>
+      <c r="I62" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="J62" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="K62" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="D63" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="E63" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="F63" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="G63" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="H63" s="16">
+        <v>2</v>
+      </c>
+      <c r="I63" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="J63" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="D64" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="E64" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="F64" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="G64" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="H64" s="18">
+        <v>2</v>
+      </c>
+      <c r="I64" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="J64" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="K64" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="D65" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="F65" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="G65" s="17" t="s">
+        <v>375</v>
+      </c>
+      <c r="H65" s="16">
+        <v>1</v>
+      </c>
+      <c r="I65" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="J49" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="K49" s="18" t="s">
+      <c r="J65" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="K65" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="D50" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="E50" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>312</v>
-      </c>
-      <c r="G50" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="H50" s="16">
-        <v>1.5</v>
-      </c>
-      <c r="I50" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="J50" s="16" t="s">
-        <v>305</v>
-      </c>
-      <c r="K50" s="16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C51" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="D51" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="E51" s="19" t="s">
-        <v>316</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>317</v>
-      </c>
-      <c r="G51" s="19" t="s">
-        <v>318</v>
-      </c>
-      <c r="H51" s="18">
-        <v>3</v>
-      </c>
-      <c r="I51" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="J51" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="K51" s="18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>319</v>
-      </c>
-      <c r="D52" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="F52" s="17" t="s">
-        <v>322</v>
-      </c>
-      <c r="G52" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="H52" s="16">
-        <v>2</v>
-      </c>
-      <c r="I52" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="J52" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="K52" s="16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C53" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="D53" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="E53" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>326</v>
-      </c>
-      <c r="G53" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="H53" s="18">
-        <v>2.5</v>
-      </c>
-      <c r="I53" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="J53" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="K53" s="18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>328</v>
-      </c>
-      <c r="D54" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="E54" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="F54" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="G54" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="H54" s="16">
-        <v>1.5</v>
-      </c>
-      <c r="I54" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="J54" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="K54" s="16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B55" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C55" s="18" t="s">
-        <v>333</v>
-      </c>
-      <c r="D55" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="E55" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="F55" s="19" t="s">
-        <v>336</v>
-      </c>
-      <c r="G55" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="H55" s="18">
-        <v>1.5</v>
-      </c>
-      <c r="I55" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="J55" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="K55" s="18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C56" s="16" t="s">
-        <v>338</v>
-      </c>
-      <c r="D56" s="17" t="s">
-        <v>339</v>
-      </c>
-      <c r="E56" s="17" t="s">
-        <v>340</v>
-      </c>
-      <c r="F56" s="17" t="s">
-        <v>341</v>
-      </c>
-      <c r="G56" s="17" t="s">
-        <v>342</v>
-      </c>
-      <c r="H56" s="16">
-        <v>2.5</v>
-      </c>
-      <c r="I56" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="J56" s="16" t="s">
-        <v>324</v>
-      </c>
-      <c r="K56" s="16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B57" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>343</v>
-      </c>
-      <c r="D57" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="E57" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="F57" s="19" t="s">
-        <v>346</v>
-      </c>
-      <c r="G57" s="19" t="s">
-        <v>347</v>
-      </c>
-      <c r="H57" s="18">
-        <v>2</v>
-      </c>
-      <c r="I57" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="J57" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="K57" s="18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>348</v>
-      </c>
-      <c r="D58" s="17" t="s">
-        <v>344</v>
-      </c>
-      <c r="E58" s="17" t="s">
-        <v>349</v>
-      </c>
-      <c r="F58" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="G58" s="17" t="s">
-        <v>351</v>
-      </c>
-      <c r="H58" s="16">
-        <v>1.5</v>
-      </c>
-      <c r="I58" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="J58" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="K58" s="16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C59" s="18" t="s">
-        <v>352</v>
-      </c>
-      <c r="D59" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="E59" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="F59" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="G59" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="H59" s="18">
-        <v>1.5</v>
-      </c>
-      <c r="I59" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="J59" s="18" t="s">
-        <v>348</v>
-      </c>
-      <c r="K59" s="18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="D60" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="E60" s="17" t="s">
-        <v>358</v>
-      </c>
-      <c r="F60" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="G60" s="17" t="s">
-        <v>360</v>
-      </c>
-      <c r="H60" s="16">
-        <v>2</v>
-      </c>
-      <c r="I60" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="J60" s="16" t="s">
-        <v>352</v>
-      </c>
-      <c r="K60" s="16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B61" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C61" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="D61" s="19" t="s">
-        <v>357</v>
-      </c>
-      <c r="E61" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="F61" s="19" t="s">
-        <v>363</v>
-      </c>
-      <c r="G61" s="19" t="s">
-        <v>364</v>
-      </c>
-      <c r="H61" s="18">
-        <v>2</v>
-      </c>
-      <c r="I61" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="J61" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="K61" s="18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C62" s="16" t="s">
-        <v>365</v>
-      </c>
-      <c r="D62" s="17" t="s">
-        <v>366</v>
-      </c>
-      <c r="E62" s="17" t="s">
-        <v>367</v>
-      </c>
-      <c r="F62" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="G62" s="17" t="s">
-        <v>369</v>
-      </c>
-      <c r="H62" s="16">
-        <v>2</v>
-      </c>
-      <c r="I62" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="J62" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="K62" s="16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B63" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C63" s="18" t="s">
-        <v>370</v>
-      </c>
-      <c r="D63" s="19" t="s">
-        <v>366</v>
-      </c>
-      <c r="E63" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="F63" s="19" t="s">
-        <v>372</v>
-      </c>
-      <c r="G63" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="H63" s="18">
-        <v>2</v>
-      </c>
-      <c r="I63" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="J63" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="K63" s="18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>374</v>
-      </c>
-      <c r="D64" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="E64" s="17" t="s">
+    <row r="66" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B66" s="33"/>
+      <c r="C66" s="33"/>
+      <c r="D66" s="33"/>
+      <c r="E66" s="33"/>
+      <c r="F66" s="33"/>
+      <c r="G66" s="33"/>
+      <c r="H66" s="21">
+        <f>SUM(H4:H65)</f>
+        <v>129.5</v>
+      </c>
+      <c r="I66" s="21" t="str">
+        <f>COUNTA(C4:C65)&amp;" görev"</f>
+        <v>62 görev</v>
+      </c>
+      <c r="J66" s="20"/>
+      <c r="K66" s="20"/>
+    </row>
+    <row r="68" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="30" t="s">
         <v>376</v>
-      </c>
-      <c r="F64" s="17" t="s">
-        <v>377</v>
-      </c>
-      <c r="G64" s="17" t="s">
-        <v>378</v>
-      </c>
-      <c r="H64" s="16">
-        <v>1</v>
-      </c>
-      <c r="I64" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="J64" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="K64" s="16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="B65" s="33"/>
-      <c r="C65" s="33"/>
-      <c r="D65" s="33"/>
-      <c r="E65" s="33"/>
-      <c r="F65" s="33"/>
-      <c r="G65" s="33"/>
-      <c r="H65" s="21">
-        <f>SUM(H4:H64)</f>
-        <v>126</v>
-      </c>
-      <c r="I65" s="21" t="str">
-        <f>COUNTA(C4:C64)&amp;" görev"</f>
-        <v>61 görev</v>
-      </c>
-      <c r="J65" s="20"/>
-      <c r="K65" s="20"/>
-    </row>
-    <row r="67" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="30" t="s">
-        <v>379</v>
-      </c>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29"/>
-      <c r="K67" s="29"/>
-    </row>
-    <row r="68" spans="1:11" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="30" t="s">
-        <v>380</v>
       </c>
       <c r="B68" s="29"/>
       <c r="C68" s="29"/>
@@ -5869,9 +5922,9 @@
       <c r="J68" s="29"/>
       <c r="K68" s="29"/>
     </row>
-    <row r="69" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="30" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B69" s="29"/>
       <c r="C69" s="29"/>
@@ -5884,9 +5937,9 @@
       <c r="J69" s="29"/>
       <c r="K69" s="29"/>
     </row>
-    <row r="70" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="30" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B70" s="29"/>
       <c r="C70" s="29"/>
@@ -5899,18 +5952,33 @@
       <c r="J70" s="29"/>
       <c r="K70" s="29"/>
     </row>
+    <row r="71" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="30" t="s">
+        <v>379</v>
+      </c>
+      <c r="B71" s="29"/>
+      <c r="C71" s="29"/>
+      <c r="D71" s="29"/>
+      <c r="E71" s="29"/>
+      <c r="F71" s="29"/>
+      <c r="G71" s="29"/>
+      <c r="H71" s="29"/>
+      <c r="I71" s="29"/>
+      <c r="J71" s="29"/>
+      <c r="K71" s="29"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K64" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A3:K65" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="7">
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A71:K71"/>
+    <mergeCell ref="A68:K68"/>
     <mergeCell ref="A70:K70"/>
-    <mergeCell ref="A67:K67"/>
+    <mergeCell ref="A2:K2"/>
     <mergeCell ref="A69:K69"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A68:K68"/>
-    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A66:G66"/>
   </mergeCells>
-  <conditionalFormatting sqref="I4:I64">
+  <conditionalFormatting sqref="I4:I45 I47:I65">
     <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"Kritik"</formula>
     </cfRule>
@@ -5918,7 +5986,7 @@
       <formula>"Yüksek"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K64">
+  <conditionalFormatting sqref="K47:K65 K4:K45">
     <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"Tamamlandı"</formula>
     </cfRule>
@@ -5930,7 +5998,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" promptTitle="Durum" prompt="Yapılacak / Devam Ediyor / Tamamlandı / Bloke" sqref="K4:K64" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" promptTitle="Durum" prompt="Yapılacak / Devam Ediyor / Tamamlandı / Bloke" sqref="K4:K45 K47:K65" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Yapılacak,Devam Ediyor,Tamamlandı,Bloke"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5957,7 +6025,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -5967,7 +6035,7 @@
     </row>
     <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -5977,19 +6045,19 @@
     </row>
     <row r="3" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>386</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>389</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>50</v>
@@ -6000,16 +6068,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="E4" s="17" t="s">
         <v>390</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>391</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>392</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>393</v>
       </c>
       <c r="F4" s="16" t="s">
         <v>200</v>
@@ -6020,16 +6088,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>186</v>
@@ -6040,16 +6108,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F6" s="16" t="s">
         <v>186</v>
@@ -6060,16 +6128,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>190</v>
@@ -6080,16 +6148,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>190</v>
@@ -6100,16 +6168,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>190</v>
@@ -6120,16 +6188,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F10" s="16" t="s">
         <v>190</v>
@@ -6140,16 +6208,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="E11" s="19" t="s">
         <v>410</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>411</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>412</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>413</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>204</v>
@@ -6160,16 +6228,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="E12" s="17" t="s">
         <v>414</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>415</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>416</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>417</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>209</v>
@@ -6180,16 +6248,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="E13" s="19" t="s">
         <v>418</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>419</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>421</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>217</v>
@@ -6200,16 +6268,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="17" t="s">
+        <v>419</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="E14" s="17" t="s">
         <v>422</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>423</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>424</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>425</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>213</v>
@@ -6220,16 +6288,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>424</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="E15" s="19" t="s">
         <v>426</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>427</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>428</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>429</v>
       </c>
       <c r="F15" s="18" t="s">
         <v>221</v>
@@ -6240,16 +6308,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F16" s="16" t="s">
         <v>226</v>
@@ -6260,16 +6328,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F17" s="18" t="s">
         <v>230</v>
@@ -6280,16 +6348,16 @@
         <v>15</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F18" s="16" t="s">
         <v>234</v>
@@ -6300,16 +6368,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>437</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="E19" s="19" t="s">
         <v>439</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>440</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>442</v>
       </c>
       <c r="F19" s="18" t="s">
         <v>238</v>
@@ -6320,16 +6388,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F20" s="16" t="s">
         <v>246</v>
@@ -6340,16 +6408,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F21" s="18" t="s">
         <v>242</v>
@@ -6360,16 +6428,16 @@
         <v>19</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F22" s="16" t="s">
         <v>242</v>
@@ -6380,16 +6448,16 @@
         <v>20</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>246</v>
@@ -6400,16 +6468,16 @@
         <v>21</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F24" s="16" t="s">
         <v>250</v>
@@ -6420,16 +6488,16 @@
         <v>22</v>
       </c>
       <c r="B25" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>456</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>457</v>
+      </c>
+      <c r="E25" s="19" t="s">
         <v>458</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>459</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>460</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>461</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>255</v>
@@ -6440,16 +6508,16 @@
         <v>23</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F26" s="16" t="s">
         <v>260</v>
@@ -6460,16 +6528,16 @@
         <v>24</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>265</v>
@@ -6483,13 +6551,13 @@
         <v>9</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F28" s="16" t="s">
         <v>269</v>
@@ -6500,16 +6568,16 @@
         <v>26</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="F29" s="18" t="s">
         <v>274</v>
@@ -6520,16 +6588,16 @@
         <v>27</v>
       </c>
       <c r="B30" s="17" t="s">
+        <v>471</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>473</v>
+      </c>
+      <c r="E30" s="17" t="s">
         <v>474</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>475</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>476</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>477</v>
       </c>
       <c r="F30" s="16" t="s">
         <v>283</v>
@@ -6540,19 +6608,19 @@
         <v>28</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -6583,7 +6651,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -6594,7 +6662,7 @@
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -6605,19 +6673,19 @@
     </row>
     <row r="3" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>484</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>50</v>
@@ -6628,19 +6696,19 @@
     </row>
     <row r="4" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>487</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>488</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="E4" s="17" t="s">
         <v>489</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>490</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>491</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>492</v>
       </c>
       <c r="F4" s="16" t="s">
         <v>99</v>
@@ -6651,19 +6719,19 @@
     </row>
     <row r="5" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
+        <v>485</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>486</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>490</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>489</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>493</v>
-      </c>
-      <c r="D5" s="18" t="s">
+      <c r="E5" s="19" t="s">
         <v>491</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>494</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>99</v>
@@ -6674,19 +6742,19 @@
     </row>
     <row r="6" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>492</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>488</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>489</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>491</v>
-      </c>
       <c r="E6" s="17" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F6" s="16" t="s">
         <v>99</v>
@@ -6697,19 +6765,19 @@
     </row>
     <row r="7" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
+        <v>485</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>486</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>494</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>489</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>497</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>491</v>
-      </c>
       <c r="E7" s="19" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>99</v>
@@ -6720,19 +6788,19 @@
     </row>
     <row r="8" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>488</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>489</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>499</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>491</v>
-      </c>
       <c r="E8" s="17" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>99</v>
@@ -6743,19 +6811,19 @@
     </row>
     <row r="9" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>99</v>
@@ -6766,19 +6834,19 @@
     </row>
     <row r="10" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D10" s="22" t="s">
+        <v>499</v>
+      </c>
+      <c r="E10" s="17" t="s">
         <v>502</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>505</v>
       </c>
       <c r="F10" s="16" t="s">
         <v>99</v>
@@ -6789,19 +6857,19 @@
     </row>
     <row r="11" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>99</v>
@@ -6812,19 +6880,19 @@
     </row>
     <row r="12" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>107</v>
@@ -6835,19 +6903,19 @@
     </row>
     <row r="13" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
+        <v>485</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>509</v>
+      </c>
+      <c r="D13" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>509</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>512</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>491</v>
-      </c>
       <c r="E13" s="19" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>107</v>
@@ -6858,19 +6926,19 @@
     </row>
     <row r="14" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="D14" s="16" t="s">
         <v>488</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>509</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>514</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>491</v>
-      </c>
       <c r="E14" s="17" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>107</v>
@@ -6881,19 +6949,19 @@
     </row>
     <row r="15" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
+        <v>485</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>513</v>
+      </c>
+      <c r="D15" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>509</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>491</v>
-      </c>
       <c r="E15" s="19" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="F15" s="18" t="s">
         <v>107</v>
@@ -6904,19 +6972,19 @@
     </row>
     <row r="16" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
+        <v>515</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>516</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>517</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="E16" s="17" t="s">
         <v>518</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>519</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>520</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>491</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>521</v>
       </c>
       <c r="F16" s="16" t="s">
         <v>107</v>
@@ -6927,19 +6995,19 @@
     </row>
     <row r="17" spans="1:7" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C17" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>488</v>
+      </c>
+      <c r="E17" s="19" t="s">
         <v>520</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>491</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>523</v>
       </c>
       <c r="F17" s="18" t="s">
         <v>111</v>
@@ -6950,19 +7018,19 @@
     </row>
     <row r="18" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>521</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="D18" s="16" t="s">
         <v>488</v>
       </c>
-      <c r="B18" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>525</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>491</v>
-      </c>
       <c r="E18" s="17" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F18" s="16" t="s">
         <v>141</v>
@@ -6973,19 +7041,19 @@
     </row>
     <row r="19" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
+        <v>485</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>521</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="D19" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>527</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>491</v>
-      </c>
       <c r="E19" s="19" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F19" s="18" t="s">
         <v>141</v>
@@ -6996,19 +7064,19 @@
     </row>
     <row r="20" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F20" s="16" t="s">
         <v>99</v>
@@ -7019,19 +7087,19 @@
     </row>
     <row r="21" spans="1:7" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
+        <v>528</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>529</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>530</v>
+      </c>
+      <c r="D21" s="24" t="s">
         <v>531</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="E21" s="19" t="s">
         <v>532</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>533</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>534</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>535</v>
       </c>
       <c r="F21" s="18" t="s">
         <v>116</v>
@@ -7042,19 +7110,19 @@
     </row>
     <row r="22" spans="1:7" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>529</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>533</v>
+      </c>
+      <c r="D22" s="24" t="s">
         <v>531</v>
       </c>
-      <c r="B22" s="17" t="s">
-        <v>532</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>536</v>
-      </c>
-      <c r="D22" s="24" t="s">
+      <c r="E22" s="17" t="s">
         <v>534</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>537</v>
       </c>
       <c r="F22" s="16" t="s">
         <v>133</v>
@@ -7065,19 +7133,19 @@
     </row>
     <row r="23" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
+        <v>528</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>535</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>536</v>
+      </c>
+      <c r="D23" s="24" t="s">
         <v>531</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>538</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>539</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>534</v>
-      </c>
       <c r="E23" s="19" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>141</v>
@@ -7088,19 +7156,19 @@
     </row>
     <row r="24" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>538</v>
+      </c>
+      <c r="D24" s="24" t="s">
         <v>531</v>
       </c>
-      <c r="B24" s="17" t="s">
-        <v>538</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>541</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>534</v>
-      </c>
       <c r="E24" s="17" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F24" s="16" t="s">
         <v>150</v>
@@ -7111,22 +7179,22 @@
     </row>
     <row r="25" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
+        <v>528</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>535</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>540</v>
+      </c>
+      <c r="D25" s="24" t="s">
         <v>531</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>538</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>543</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>534</v>
-      </c>
       <c r="E25" s="19" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G25" s="18" t="s">
         <v>104</v>
@@ -7134,19 +7202,19 @@
     </row>
     <row r="26" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>543</v>
+      </c>
+      <c r="D26" s="24" t="s">
         <v>531</v>
       </c>
-      <c r="B26" s="17" t="s">
-        <v>545</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>546</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>534</v>
-      </c>
       <c r="E26" s="17" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="F26" s="16" t="s">
         <v>129</v>
@@ -7157,19 +7225,19 @@
     </row>
     <row r="27" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
+        <v>528</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>542</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="D27" s="24" t="s">
         <v>531</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>545</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>548</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>534</v>
-      </c>
       <c r="E27" s="19" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>129</v>
@@ -7180,19 +7248,19 @@
     </row>
     <row r="28" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="F28" s="16" t="s">
         <v>141</v>
@@ -7203,19 +7271,19 @@
     </row>
     <row r="29" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="18" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F29" s="18" t="s">
         <v>125</v>
@@ -7226,22 +7294,22 @@
     </row>
     <row r="30" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
+        <v>552</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>553</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>554</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>531</v>
+      </c>
+      <c r="E30" s="17" t="s">
         <v>555</v>
       </c>
-      <c r="B30" s="17" t="s">
-        <v>556</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>557</v>
-      </c>
-      <c r="D30" s="24" t="s">
-        <v>534</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>558</v>
-      </c>
       <c r="F30" s="16" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G30" s="16" t="s">
         <v>104</v>
@@ -7249,19 +7317,19 @@
     </row>
     <row r="31" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="18" t="s">
+        <v>556</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>557</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>558</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>488</v>
+      </c>
+      <c r="E31" s="19" t="s">
         <v>559</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>560</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>561</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>491</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>562</v>
       </c>
       <c r="F31" s="18" t="s">
         <v>111</v>
@@ -7272,19 +7340,19 @@
     </row>
     <row r="32" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B32" s="17" t="s">
+        <v>557</v>
+      </c>
+      <c r="C32" s="17" t="s">
         <v>560</v>
       </c>
-      <c r="C32" s="17" t="s">
-        <v>563</v>
-      </c>
       <c r="D32" s="16" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="F32" s="16" t="s">
         <v>99</v>
@@ -7321,7 +7389,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -7332,7 +7400,7 @@
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -7343,39 +7411,39 @@
     </row>
     <row r="3" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>570</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C4" s="25">
         <v>40</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="E4" s="25">
         <v>6</v>
@@ -7385,21 +7453,21 @@
         <v>408</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C5" s="26">
         <v>35</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E5" s="26">
         <v>2</v>
@@ -7409,21 +7477,21 @@
         <v>396</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C6" s="25">
         <v>12</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E6" s="25">
         <v>0</v>
@@ -7433,21 +7501,21 @@
         <v>144</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="C7" s="26">
         <v>15</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E7" s="26">
         <v>0</v>
@@ -7457,21 +7525,21 @@
         <v>180</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C8" s="25">
         <v>10</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E8" s="25">
         <v>0</v>
@@ -7481,21 +7549,21 @@
         <v>120</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="16.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C9" s="26">
         <v>20</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E9" s="26">
         <v>0</v>
@@ -7505,21 +7573,21 @@
         <v>240</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C10" s="25">
         <v>8</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E10" s="25">
         <v>0</v>
@@ -7529,21 +7597,21 @@
         <v>96</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C11" s="26">
         <v>5</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E11" s="26">
         <v>0</v>
@@ -7553,21 +7621,21 @@
         <v>60</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="16.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C12" s="25">
         <v>26</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E12" s="25">
         <v>0</v>
@@ -7577,21 +7645,21 @@
         <v>312</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C13" s="26">
         <v>5</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E13" s="26">
         <v>0</v>
@@ -7601,21 +7669,21 @@
         <v>60</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="16.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C14" s="25">
         <v>1.5</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E14" s="25">
         <v>1.5</v>
@@ -7625,21 +7693,21 @@
         <v>0</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="16.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C15" s="26">
         <v>2.08</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="E15" s="26">
         <v>2.08</v>
@@ -7649,21 +7717,21 @@
         <v>0</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C16" s="25">
         <v>8.25</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E16" s="25">
         <v>8.25</v>
@@ -7673,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -7686,7 +7754,7 @@
         <v>187.83</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="E17" s="27">
         <f>SUM(E4:E16)</f>
@@ -7699,8 +7767,8 @@
       <c r="G17" s="9"/>
     </row>
     <row r="19" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="34" t="s">
-        <v>618</v>
+      <c r="A19" s="36" t="s">
+        <v>615</v>
       </c>
       <c r="B19" s="29"/>
       <c r="C19" s="29"/>
@@ -7710,8 +7778,8 @@
       <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="34" t="s">
-        <v>619</v>
+      <c r="A20" s="36" t="s">
+        <v>616</v>
       </c>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
@@ -7721,8 +7789,8 @@
       <c r="G20" s="29"/>
     </row>
     <row r="21" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="34" t="s">
-        <v>620</v>
+      <c r="A21" s="36" t="s">
+        <v>617</v>
       </c>
       <c r="B21" s="29"/>
       <c r="C21" s="29"/>
@@ -7759,7 +7827,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -7768,7 +7836,7 @@
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -7777,24 +7845,24 @@
     </row>
     <row r="3" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>624</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>626</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>155</v>
@@ -7803,15 +7871,15 @@
         <v>155</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>155</v>
@@ -7820,15 +7888,15 @@
         <v>254</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>155</v>
@@ -7837,15 +7905,15 @@
         <v>155</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>155</v>
@@ -7854,15 +7922,15 @@
         <v>155</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>254</v>
@@ -7871,15 +7939,15 @@
         <v>155</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>254</v>
@@ -7888,15 +7956,15 @@
         <v>254</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>254</v>
@@ -7905,15 +7973,15 @@
         <v>254</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>254</v>
@@ -7922,15 +7990,15 @@
         <v>254</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>254</v>
@@ -7939,15 +8007,15 @@
         <v>155</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B13" s="18" t="s">
         <v>155</v>
@@ -7956,15 +8024,15 @@
         <v>155</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>254</v>
@@ -7973,15 +8041,15 @@
         <v>254</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>254</v>
@@ -7990,10 +8058,10 @@
         <v>254</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -8036,7 +8104,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -8047,7 +8115,7 @@
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -8058,7 +8126,7 @@
     </row>
     <row r="3" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>96</v>
@@ -8067,269 +8135,269 @@
         <v>91</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>667</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
+        <v>668</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>669</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>670</v>
+      </c>
+      <c r="D4" s="17" t="s">
         <v>671</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="E4" s="17" t="s">
         <v>672</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="F4" s="17" t="s">
         <v>673</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="G4" s="16" t="s">
         <v>674</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>675</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>676</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="C5" s="19" t="s">
+        <v>675</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>676</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>677</v>
+      </c>
+      <c r="F5" s="19" t="s">
         <v>678</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>679</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>680</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>681</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>155</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D6" s="17" t="s">
+        <v>680</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>681</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>682</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>683</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>684</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>685</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>155</v>
       </c>
       <c r="C7" s="19" t="s">
+        <v>684</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>685</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>686</v>
+      </c>
+      <c r="F7" s="19" t="s">
         <v>687</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>688</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>689</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>690</v>
-      </c>
       <c r="G7" s="18" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>155</v>
       </c>
       <c r="C8" s="17" t="s">
+        <v>688</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>689</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>690</v>
+      </c>
+      <c r="F8" s="17" t="s">
         <v>691</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>692</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>693</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>694</v>
-      </c>
       <c r="G8" s="16" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>254</v>
       </c>
       <c r="C9" s="19" t="s">
+        <v>692</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>693</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>694</v>
+      </c>
+      <c r="F9" s="19" t="s">
         <v>695</v>
       </c>
-      <c r="D9" s="19" t="s">
-        <v>696</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>697</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>698</v>
-      </c>
       <c r="G9" s="18" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>254</v>
       </c>
       <c r="C10" s="17" t="s">
+        <v>696</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>697</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>698</v>
+      </c>
+      <c r="F10" s="17" t="s">
         <v>699</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="G10" s="16" t="s">
         <v>700</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>701</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>702</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>254</v>
       </c>
       <c r="C11" s="19" t="s">
+        <v>701</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>702</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>703</v>
+      </c>
+      <c r="F11" s="19" t="s">
         <v>704</v>
       </c>
-      <c r="D11" s="19" t="s">
-        <v>705</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>706</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>707</v>
-      </c>
       <c r="G11" s="18" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>155</v>
       </c>
       <c r="C12" s="17" t="s">
+        <v>706</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>707</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>708</v>
+      </c>
+      <c r="F12" s="17" t="s">
         <v>709</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="G12" s="16" t="s">
         <v>710</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>711</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>712</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B13" s="18" t="s">
+        <v>711</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>712</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>713</v>
+      </c>
+      <c r="E13" s="19" t="s">
         <v>714</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="F13" s="19" t="s">
         <v>715</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="G13" s="18" t="s">
         <v>716</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>717</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>718</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>717</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>718</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>719</v>
+      </c>
+      <c r="F14" s="17" t="s">
         <v>720</v>
       </c>
-      <c r="D14" s="17" t="s">
-        <v>721</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>722</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>723</v>
-      </c>
       <c r="G14" s="16" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
+++ b/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekin\Desktop\FDN\kalori\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34CD7E68-5065-4A11-A3A9-D59F6E0F8081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D22415-7E0E-45F7-A2FE-DB33D2E6EDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2481,6 +2481,18 @@
     <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -2495,25 +2507,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2927,24 +2927,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2955,181 +2955,181 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
     </row>
     <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
     </row>
     <row r="7" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
     </row>
     <row r="8" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
     </row>
     <row r="9" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
     </row>
     <row r="10" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
     </row>
     <row r="11" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
     </row>
     <row r="12" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
     </row>
     <row r="13" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
     </row>
     <row r="14" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
     </row>
     <row r="15" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
     </row>
     <row r="16" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
     </row>
     <row r="17" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
     </row>
     <row r="18" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
     </row>
     <row r="19" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -3194,11 +3194,11 @@
       </c>
       <c r="D24" s="6">
         <f>SUMIFS('Sprint Plani'!$H$4:$H$65,'Sprint Plani'!$A$4:$A$65,$A24,'Sprint Plani'!$K$4:$K$65,"Tamamlandı")</f>
-        <v>7.5</v>
+        <v>13</v>
       </c>
       <c r="E24" s="7">
         <f>IFERROR($D24/$C24,0)</f>
-        <v>0.15306122448979592</v>
+        <v>0.26530612244897961</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>43</v>
@@ -3242,11 +3242,11 @@
       </c>
       <c r="D26" s="10">
         <f>SUM(D23:D25)</f>
-        <v>43.5</v>
+        <v>49</v>
       </c>
       <c r="E26" s="11">
         <f>IFERROR(D26/C26,0)</f>
-        <v>0.3359073359073359</v>
+        <v>0.3783783783783784</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>47</v>
@@ -3531,85 +3531,77 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
+      <c r="B46" s="33"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="33"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="33"/>
     </row>
     <row r="47" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="36" t="s">
+      <c r="A47" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="33"/>
+      <c r="E47" s="33"/>
+      <c r="F47" s="33"/>
     </row>
     <row r="48" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="36" t="s">
+      <c r="A48" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
+      <c r="B48" s="33"/>
+      <c r="C48" s="33"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="33"/>
+      <c r="F48" s="33"/>
     </row>
     <row r="49" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="36" t="s">
+      <c r="A49" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
+      <c r="B49" s="33"/>
+      <c r="C49" s="33"/>
+      <c r="D49" s="33"/>
+      <c r="E49" s="33"/>
+      <c r="F49" s="33"/>
     </row>
     <row r="50" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="36" t="s">
+      <c r="A50" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
-      <c r="E50" s="29"/>
-      <c r="F50" s="29"/>
+      <c r="B50" s="33"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="33"/>
+      <c r="F50" s="33"/>
     </row>
     <row r="51" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="36" t="s">
+      <c r="A51" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
+      <c r="B51" s="33"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="33"/>
+      <c r="E51" s="33"/>
+      <c r="F51" s="33"/>
     </row>
     <row r="52" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="36" t="s">
+      <c r="A52" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
+      <c r="B52" s="33"/>
+      <c r="C52" s="33"/>
+      <c r="D52" s="33"/>
+      <c r="E52" s="33"/>
+      <c r="F52" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="B16:F16"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A52:F52"/>
@@ -3626,6 +3618,14 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B16:F16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3652,34 +3652,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
     </row>
     <row r="3" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -4381,26 +4381,26 @@
         <v>721</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="38" customFormat="1" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="37" t="s">
+    <row r="23" spans="1:11" s="29" customFormat="1" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="28" t="s">
         <v>723</v>
       </c>
-      <c r="D23" s="37" t="s">
+      <c r="D23" s="28" t="s">
         <v>724</v>
       </c>
-      <c r="E23" s="37" t="s">
+      <c r="E23" s="28" t="s">
         <v>725</v>
       </c>
-      <c r="F23" s="40" t="s">
+      <c r="F23" s="31" t="s">
         <v>726</v>
       </c>
-      <c r="G23" s="37" t="s">
+      <c r="G23" s="28" t="s">
         <v>727</v>
       </c>
       <c r="H23" s="18">
@@ -4448,7 +4448,7 @@
         <v>723</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4483,7 +4483,7 @@
         <v>190</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
@@ -4518,7 +4518,7 @@
         <v>190</v>
       </c>
       <c r="K26" s="18" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5186,38 +5186,38 @@
         <v>106</v>
       </c>
     </row>
-    <row r="46" spans="1:11" s="38" customFormat="1" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="37" t="s">
+    <row r="46" spans="1:11" s="29" customFormat="1" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="37" t="s">
+      <c r="B46" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="C46" s="37" t="s">
+      <c r="C46" s="28" t="s">
         <v>287</v>
       </c>
-      <c r="D46" s="37" t="s">
+      <c r="D46" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="E46" s="37" t="s">
+      <c r="E46" s="28" t="s">
         <v>728</v>
       </c>
-      <c r="F46" s="37" t="s">
+      <c r="F46" s="28" t="s">
         <v>729</v>
       </c>
-      <c r="G46" s="37" t="s">
+      <c r="G46" s="28" t="s">
         <v>730</v>
       </c>
-      <c r="H46" s="39">
+      <c r="H46" s="30">
         <v>1.5</v>
       </c>
-      <c r="I46" s="37" t="s">
+      <c r="I46" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="J46" s="37" t="s">
+      <c r="J46" s="28" t="s">
         <v>731</v>
       </c>
-      <c r="K46" s="37" t="s">
+      <c r="K46" s="28" t="s">
         <v>106</v>
       </c>
     </row>
@@ -5887,15 +5887,15 @@
       </c>
     </row>
     <row r="66" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="32" t="s">
+      <c r="A66" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="B66" s="33"/>
-      <c r="C66" s="33"/>
-      <c r="D66" s="33"/>
-      <c r="E66" s="33"/>
-      <c r="F66" s="33"/>
-      <c r="G66" s="33"/>
+      <c r="B66" s="37"/>
+      <c r="C66" s="37"/>
+      <c r="D66" s="37"/>
+      <c r="E66" s="37"/>
+      <c r="F66" s="37"/>
+      <c r="G66" s="37"/>
       <c r="H66" s="21">
         <f>SUM(H4:H65)</f>
         <v>129.5</v>
@@ -5908,64 +5908,64 @@
       <c r="K66" s="20"/>
     </row>
     <row r="68" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="30" t="s">
+      <c r="A68" s="34" t="s">
         <v>376</v>
       </c>
-      <c r="B68" s="29"/>
-      <c r="C68" s="29"/>
-      <c r="D68" s="29"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="29"/>
-      <c r="G68" s="29"/>
-      <c r="H68" s="29"/>
-      <c r="I68" s="29"/>
-      <c r="J68" s="29"/>
-      <c r="K68" s="29"/>
+      <c r="B68" s="33"/>
+      <c r="C68" s="33"/>
+      <c r="D68" s="33"/>
+      <c r="E68" s="33"/>
+      <c r="F68" s="33"/>
+      <c r="G68" s="33"/>
+      <c r="H68" s="33"/>
+      <c r="I68" s="33"/>
+      <c r="J68" s="33"/>
+      <c r="K68" s="33"/>
     </row>
     <row r="69" spans="1:11" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="30" t="s">
+      <c r="A69" s="34" t="s">
         <v>377</v>
       </c>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="29"/>
-      <c r="I69" s="29"/>
-      <c r="J69" s="29"/>
-      <c r="K69" s="29"/>
+      <c r="B69" s="33"/>
+      <c r="C69" s="33"/>
+      <c r="D69" s="33"/>
+      <c r="E69" s="33"/>
+      <c r="F69" s="33"/>
+      <c r="G69" s="33"/>
+      <c r="H69" s="33"/>
+      <c r="I69" s="33"/>
+      <c r="J69" s="33"/>
+      <c r="K69" s="33"/>
     </row>
     <row r="70" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="30" t="s">
+      <c r="A70" s="34" t="s">
         <v>378</v>
       </c>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="29"/>
-      <c r="K70" s="29"/>
+      <c r="B70" s="33"/>
+      <c r="C70" s="33"/>
+      <c r="D70" s="33"/>
+      <c r="E70" s="33"/>
+      <c r="F70" s="33"/>
+      <c r="G70" s="33"/>
+      <c r="H70" s="33"/>
+      <c r="I70" s="33"/>
+      <c r="J70" s="33"/>
+      <c r="K70" s="33"/>
     </row>
     <row r="71" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="30" t="s">
+      <c r="A71" s="34" t="s">
         <v>379</v>
       </c>
-      <c r="B71" s="29"/>
-      <c r="C71" s="29"/>
-      <c r="D71" s="29"/>
-      <c r="E71" s="29"/>
-      <c r="F71" s="29"/>
-      <c r="G71" s="29"/>
-      <c r="H71" s="29"/>
-      <c r="I71" s="29"/>
-      <c r="J71" s="29"/>
-      <c r="K71" s="29"/>
+      <c r="B71" s="33"/>
+      <c r="C71" s="33"/>
+      <c r="D71" s="33"/>
+      <c r="E71" s="33"/>
+      <c r="F71" s="33"/>
+      <c r="G71" s="33"/>
+      <c r="H71" s="33"/>
+      <c r="I71" s="33"/>
+      <c r="J71" s="33"/>
+      <c r="K71" s="33"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:K65" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
@@ -5986,7 +5986,7 @@
       <formula>"Yüksek"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K47:K65 K4:K45">
+  <conditionalFormatting sqref="K4:K45 K47:K65">
     <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"Tamamlandı"</formula>
     </cfRule>
@@ -6024,24 +6024,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>380</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>381</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
     </row>
     <row r="3" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -6650,26 +6650,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>478</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>479</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="3" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -7388,26 +7388,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>562</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>563</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="3" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -7767,37 +7767,37 @@
       <c r="G17" s="9"/>
     </row>
     <row r="19" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="38" t="s">
         <v>615</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
     </row>
     <row r="20" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="38" t="s">
         <v>616</v>
       </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
     </row>
     <row r="21" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="38" t="s">
         <v>617</v>
       </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7826,22 +7826,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>618</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>619</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
     </row>
     <row r="3" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -8103,26 +8103,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>661</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>662</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="3" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">

--- a/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
+++ b/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekin\Desktop\FDN\kalori\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D22415-7E0E-45F7-A2FE-DB33D2E6EDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BC5606-B111-4ED7-80D6-7C7EEF140F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2507,13 +2507,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2955,181 +2955,181 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
     </row>
     <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
     </row>
     <row r="7" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
     </row>
     <row r="8" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
     </row>
     <row r="9" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
     </row>
     <row r="10" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
     </row>
     <row r="11" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
     </row>
     <row r="12" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
     </row>
     <row r="13" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
     </row>
     <row r="14" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
     </row>
     <row r="15" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
     </row>
     <row r="16" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
     </row>
     <row r="17" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
     </row>
     <row r="18" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
     </row>
     <row r="19" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -3194,11 +3194,11 @@
       </c>
       <c r="D24" s="6">
         <f>SUMIFS('Sprint Plani'!$H$4:$H$65,'Sprint Plani'!$A$4:$A$65,$A24,'Sprint Plani'!$K$4:$K$65,"Tamamlandı")</f>
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E24" s="7">
         <f>IFERROR($D24/$C24,0)</f>
-        <v>0.26530612244897961</v>
+        <v>0.40816326530612246</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>43</v>
@@ -3242,11 +3242,11 @@
       </c>
       <c r="D26" s="10">
         <f>SUM(D23:D25)</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E26" s="11">
         <f>IFERROR(D26/C26,0)</f>
-        <v>0.3783783783783784</v>
+        <v>0.43243243243243246</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>47</v>
@@ -3531,7 +3531,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="38" t="s">
+      <c r="A46" s="40" t="s">
         <v>81</v>
       </c>
       <c r="B46" s="33"/>
@@ -3541,7 +3541,7 @@
       <c r="F46" s="33"/>
     </row>
     <row r="47" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="38" t="s">
+      <c r="A47" s="40" t="s">
         <v>82</v>
       </c>
       <c r="B47" s="33"/>
@@ -3551,7 +3551,7 @@
       <c r="F47" s="33"/>
     </row>
     <row r="48" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="38" t="s">
+      <c r="A48" s="40" t="s">
         <v>83</v>
       </c>
       <c r="B48" s="33"/>
@@ -3561,7 +3561,7 @@
       <c r="F48" s="33"/>
     </row>
     <row r="49" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="38" t="s">
+      <c r="A49" s="40" t="s">
         <v>84</v>
       </c>
       <c r="B49" s="33"/>
@@ -3571,7 +3571,7 @@
       <c r="F49" s="33"/>
     </row>
     <row r="50" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="38" t="s">
+      <c r="A50" s="40" t="s">
         <v>85</v>
       </c>
       <c r="B50" s="33"/>
@@ -3581,7 +3581,7 @@
       <c r="F50" s="33"/>
     </row>
     <row r="51" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="38" t="s">
+      <c r="A51" s="40" t="s">
         <v>86</v>
       </c>
       <c r="B51" s="33"/>
@@ -3591,7 +3591,7 @@
       <c r="F51" s="33"/>
     </row>
     <row r="52" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="38" t="s">
+      <c r="A52" s="40" t="s">
         <v>87</v>
       </c>
       <c r="B52" s="33"/>
@@ -3602,6 +3602,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A52:F52"/>
@@ -3618,14 +3626,6 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="B16:F16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4553,7 +4553,7 @@
         <v>176</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -4588,7 +4588,7 @@
         <v>204</v>
       </c>
       <c r="K28" s="18" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4623,7 +4623,7 @@
         <v>209</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -7767,7 +7767,7 @@
       <c r="G17" s="9"/>
     </row>
     <row r="19" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="40" t="s">
         <v>615</v>
       </c>
       <c r="B19" s="33"/>
@@ -7778,7 +7778,7 @@
       <c r="G19" s="33"/>
     </row>
     <row r="20" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="40" t="s">
         <v>616</v>
       </c>
       <c r="B20" s="33"/>
@@ -7789,7 +7789,7 @@
       <c r="G20" s="33"/>
     </row>
     <row r="21" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="40" t="s">
         <v>617</v>
       </c>
       <c r="B21" s="33"/>

--- a/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
+++ b/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekin\Desktop\FDN\kalori\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BC5606-B111-4ED7-80D6-7C7EEF140F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534B8F8C-E7E3-4485-976B-125A3D2D2D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2507,13 +2507,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2955,181 +2955,181 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
     </row>
     <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
     </row>
     <row r="7" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
     </row>
     <row r="8" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
     </row>
     <row r="9" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
     </row>
     <row r="10" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
     </row>
     <row r="11" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
     </row>
     <row r="12" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
     </row>
     <row r="13" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
     </row>
     <row r="14" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
     </row>
     <row r="15" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
     </row>
     <row r="16" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
     </row>
     <row r="17" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
     </row>
     <row r="18" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
     </row>
     <row r="19" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -3194,11 +3194,11 @@
       </c>
       <c r="D24" s="6">
         <f>SUMIFS('Sprint Plani'!$H$4:$H$65,'Sprint Plani'!$A$4:$A$65,$A24,'Sprint Plani'!$K$4:$K$65,"Tamamlandı")</f>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E24" s="7">
         <f>IFERROR($D24/$C24,0)</f>
-        <v>0.40816326530612246</v>
+        <v>0.51020408163265307</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>43</v>
@@ -3242,11 +3242,11 @@
       </c>
       <c r="D26" s="10">
         <f>SUM(D23:D25)</f>
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E26" s="11">
         <f>IFERROR(D26/C26,0)</f>
-        <v>0.43243243243243246</v>
+        <v>0.47104247104247104</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>47</v>
@@ -3531,7 +3531,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="40" t="s">
+      <c r="A46" s="38" t="s">
         <v>81</v>
       </c>
       <c r="B46" s="33"/>
@@ -3541,7 +3541,7 @@
       <c r="F46" s="33"/>
     </row>
     <row r="47" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="40" t="s">
+      <c r="A47" s="38" t="s">
         <v>82</v>
       </c>
       <c r="B47" s="33"/>
@@ -3551,7 +3551,7 @@
       <c r="F47" s="33"/>
     </row>
     <row r="48" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="40" t="s">
+      <c r="A48" s="38" t="s">
         <v>83</v>
       </c>
       <c r="B48" s="33"/>
@@ -3561,7 +3561,7 @@
       <c r="F48" s="33"/>
     </row>
     <row r="49" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="40" t="s">
+      <c r="A49" s="38" t="s">
         <v>84</v>
       </c>
       <c r="B49" s="33"/>
@@ -3571,7 +3571,7 @@
       <c r="F49" s="33"/>
     </row>
     <row r="50" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="40" t="s">
+      <c r="A50" s="38" t="s">
         <v>85</v>
       </c>
       <c r="B50" s="33"/>
@@ -3581,7 +3581,7 @@
       <c r="F50" s="33"/>
     </row>
     <row r="51" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="40" t="s">
+      <c r="A51" s="38" t="s">
         <v>86</v>
       </c>
       <c r="B51" s="33"/>
@@ -3591,7 +3591,7 @@
       <c r="F51" s="33"/>
     </row>
     <row r="52" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="40" t="s">
+      <c r="A52" s="38" t="s">
         <v>87</v>
       </c>
       <c r="B52" s="33"/>
@@ -3602,14 +3602,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="B16:F16"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A52:F52"/>
@@ -3626,6 +3618,14 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B16:F16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4658,7 +4658,7 @@
         <v>213</v>
       </c>
       <c r="K30" s="18" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4693,7 +4693,7 @@
         <v>176</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -7767,7 +7767,7 @@
       <c r="G17" s="9"/>
     </row>
     <row r="19" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="38" t="s">
         <v>615</v>
       </c>
       <c r="B19" s="33"/>
@@ -7778,7 +7778,7 @@
       <c r="G19" s="33"/>
     </row>
     <row r="20" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="38" t="s">
         <v>616</v>
       </c>
       <c r="B20" s="33"/>
@@ -7789,7 +7789,7 @@
       <c r="G20" s="33"/>
     </row>
     <row r="21" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="38" t="s">
         <v>617</v>
       </c>
       <c r="B21" s="33"/>

--- a/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
+++ b/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekin\Desktop\FDN\kalori\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534B8F8C-E7E3-4485-976B-125A3D2D2D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E3C045-5221-451C-9EE6-9297DFBB44A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="733">
   <si>
     <t>OZET DASHBOARD  |  Kalan 14 Is Gunu</t>
   </si>
@@ -2264,6 +2264,9 @@
   </si>
   <si>
     <t>W3-T02B, W3-T09</t>
+  </si>
+  <si>
+    <t>Bloke</t>
   </si>
 </sst>
 </file>
@@ -2507,13 +2510,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2955,181 +2958,181 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
     </row>
     <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
     </row>
     <row r="7" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
     </row>
     <row r="8" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
     </row>
     <row r="9" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
     </row>
     <row r="10" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
     </row>
     <row r="11" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
     </row>
     <row r="12" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
     </row>
     <row r="13" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
     </row>
     <row r="14" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
     </row>
     <row r="15" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
     </row>
     <row r="16" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
     </row>
     <row r="17" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
     </row>
     <row r="18" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
     </row>
     <row r="19" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -3194,11 +3197,11 @@
       </c>
       <c r="D24" s="6">
         <f>SUMIFS('Sprint Plani'!$H$4:$H$65,'Sprint Plani'!$A$4:$A$65,$A24,'Sprint Plani'!$K$4:$K$65,"Tamamlandı")</f>
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E24" s="7">
         <f>IFERROR($D24/$C24,0)</f>
-        <v>0.51020408163265307</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>43</v>
@@ -3242,11 +3245,11 @@
       </c>
       <c r="D26" s="10">
         <f>SUM(D23:D25)</f>
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E26" s="11">
         <f>IFERROR(D26/C26,0)</f>
-        <v>0.47104247104247104</v>
+        <v>0.60231660231660233</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>47</v>
@@ -3531,7 +3534,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="38" t="s">
+      <c r="A46" s="40" t="s">
         <v>81</v>
       </c>
       <c r="B46" s="33"/>
@@ -3541,7 +3544,7 @@
       <c r="F46" s="33"/>
     </row>
     <row r="47" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="38" t="s">
+      <c r="A47" s="40" t="s">
         <v>82</v>
       </c>
       <c r="B47" s="33"/>
@@ -3551,7 +3554,7 @@
       <c r="F47" s="33"/>
     </row>
     <row r="48" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="38" t="s">
+      <c r="A48" s="40" t="s">
         <v>83</v>
       </c>
       <c r="B48" s="33"/>
@@ -3561,7 +3564,7 @@
       <c r="F48" s="33"/>
     </row>
     <row r="49" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="38" t="s">
+      <c r="A49" s="40" t="s">
         <v>84</v>
       </c>
       <c r="B49" s="33"/>
@@ -3571,7 +3574,7 @@
       <c r="F49" s="33"/>
     </row>
     <row r="50" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="38" t="s">
+      <c r="A50" s="40" t="s">
         <v>85</v>
       </c>
       <c r="B50" s="33"/>
@@ -3581,7 +3584,7 @@
       <c r="F50" s="33"/>
     </row>
     <row r="51" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="38" t="s">
+      <c r="A51" s="40" t="s">
         <v>86</v>
       </c>
       <c r="B51" s="33"/>
@@ -3591,7 +3594,7 @@
       <c r="F51" s="33"/>
     </row>
     <row r="52" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="38" t="s">
+      <c r="A52" s="40" t="s">
         <v>87</v>
       </c>
       <c r="B52" s="33"/>
@@ -3602,6 +3605,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A52:F52"/>
@@ -3618,14 +3629,6 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="B16:F16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4727,8 +4730,8 @@
       <c r="J32" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="K32" s="18" t="s">
-        <v>106</v>
+      <c r="K32" s="16" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4763,7 +4766,7 @@
         <v>221</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4797,8 +4800,8 @@
       <c r="J34" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="K34" s="18" t="s">
-        <v>106</v>
+      <c r="K34" s="16" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4833,7 +4836,7 @@
         <v>176</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -4868,7 +4871,7 @@
         <v>238</v>
       </c>
       <c r="K36" s="18" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4902,8 +4905,8 @@
       <c r="J37" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="K37" s="16" t="s">
-        <v>106</v>
+      <c r="K37" s="18" t="s">
+        <v>732</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4938,7 +4941,7 @@
         <v>246</v>
       </c>
       <c r="K38" s="18" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4973,7 +4976,7 @@
         <v>176</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -5008,7 +5011,7 @@
         <v>156</v>
       </c>
       <c r="K40" s="18" t="s">
-        <v>106</v>
+        <v>732</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5042,8 +5045,8 @@
       <c r="J41" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="K41" s="16" t="s">
-        <v>106</v>
+      <c r="K41" s="18" t="s">
+        <v>732</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5078,7 +5081,7 @@
         <v>217</v>
       </c>
       <c r="K42" s="18" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="79.650000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -5986,7 +5989,7 @@
       <formula>"Yüksek"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K45 K47:K65">
+  <conditionalFormatting sqref="K47:K65 K4:K45">
     <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"Tamamlandı"</formula>
     </cfRule>
@@ -5998,7 +6001,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" promptTitle="Durum" prompt="Yapılacak / Devam Ediyor / Tamamlandı / Bloke" sqref="K4:K45 K47:K65" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" promptTitle="Durum" prompt="Yapılacak / Devam Ediyor / Tamamlandı / Bloke" sqref="K47:K65 K4:K45" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Yapılacak,Devam Ediyor,Tamamlandı,Bloke"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7767,7 +7770,7 @@
       <c r="G17" s="9"/>
     </row>
     <row r="19" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="40" t="s">
         <v>615</v>
       </c>
       <c r="B19" s="33"/>
@@ -7778,7 +7781,7 @@
       <c r="G19" s="33"/>
     </row>
     <row r="20" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="40" t="s">
         <v>616</v>
       </c>
       <c r="B20" s="33"/>
@@ -7789,7 +7792,7 @@
       <c r="G20" s="33"/>
     </row>
     <row r="21" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="40" t="s">
         <v>617</v>
       </c>
       <c r="B21" s="33"/>

--- a/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
+++ b/docs/Kalori_Sayaci_Kalan_14_Gun_Plani.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekin\Desktop\FDN\kalori\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E3C045-5221-451C-9EE6-9297DFBB44A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48099774-C326-4DE2-9E1C-C7856E30C7A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2510,13 +2510,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2958,181 +2958,181 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
     </row>
     <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
     </row>
     <row r="7" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
     </row>
     <row r="8" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
     </row>
     <row r="9" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
     </row>
     <row r="10" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
     </row>
     <row r="11" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
     </row>
     <row r="12" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
     </row>
     <row r="13" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
     </row>
     <row r="14" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
     </row>
     <row r="15" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
     </row>
     <row r="16" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
     </row>
     <row r="17" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
     </row>
     <row r="18" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
     </row>
     <row r="19" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -3221,11 +3221,11 @@
       </c>
       <c r="D25" s="6">
         <f>SUMIFS('Sprint Plani'!$H$4:$H$65,'Sprint Plani'!$A$4:$A$65,$A25,'Sprint Plani'!$K$4:$K$65,"Tamamlandı")</f>
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="E25" s="7">
         <f>IFERROR($D25/$C25,0)</f>
-        <v>0</v>
+        <v>0.34831460674157305</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>45</v>
@@ -3245,11 +3245,11 @@
       </c>
       <c r="D26" s="10">
         <f>SUM(D23:D25)</f>
-        <v>78</v>
+        <v>93.5</v>
       </c>
       <c r="E26" s="11">
         <f>IFERROR(D26/C26,0)</f>
-        <v>0.60231660231660233</v>
+        <v>0.72200772200772201</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>47</v>
@@ -3534,7 +3534,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="40" t="s">
+      <c r="A46" s="38" t="s">
         <v>81</v>
       </c>
       <c r="B46" s="33"/>
@@ -3544,7 +3544,7 @@
       <c r="F46" s="33"/>
     </row>
     <row r="47" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="40" t="s">
+      <c r="A47" s="38" t="s">
         <v>82</v>
       </c>
       <c r="B47" s="33"/>
@@ -3554,7 +3554,7 @@
       <c r="F47" s="33"/>
     </row>
     <row r="48" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="40" t="s">
+      <c r="A48" s="38" t="s">
         <v>83</v>
       </c>
       <c r="B48" s="33"/>
@@ -3564,7 +3564,7 @@
       <c r="F48" s="33"/>
     </row>
     <row r="49" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="40" t="s">
+      <c r="A49" s="38" t="s">
         <v>84</v>
       </c>
       <c r="B49" s="33"/>
@@ -3574,7 +3574,7 @@
       <c r="F49" s="33"/>
     </row>
     <row r="50" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="40" t="s">
+      <c r="A50" s="38" t="s">
         <v>85</v>
       </c>
       <c r="B50" s="33"/>
@@ -3584,7 +3584,7 @@
       <c r="F50" s="33"/>
     </row>
     <row r="51" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="40" t="s">
+      <c r="A51" s="38" t="s">
         <v>86</v>
       </c>
       <c r="B51" s="33"/>
@@ -3594,7 +3594,7 @@
       <c r="F51" s="33"/>
     </row>
     <row r="52" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="40" t="s">
+      <c r="A52" s="38" t="s">
         <v>87</v>
       </c>
       <c r="B52" s="33"/>
@@ -3605,14 +3605,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="B16:F16"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A52:F52"/>
@@ -3629,6 +3621,14 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B16:F16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5115,8 +5115,8 @@
       <c r="J43" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="K43" s="16" t="s">
-        <v>106</v>
+      <c r="K43" s="18" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="41.85" customHeight="1" x14ac:dyDescent="0.3">
@@ -5151,7 +5151,7 @@
         <v>274</v>
       </c>
       <c r="K44" s="18" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5185,8 +5185,8 @@
       <c r="J45" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="K45" s="16" t="s">
-        <v>106</v>
+      <c r="K45" s="18" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="29" customFormat="1" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5220,8 +5220,8 @@
       <c r="J46" s="28" t="s">
         <v>731</v>
       </c>
-      <c r="K46" s="28" t="s">
-        <v>106</v>
+      <c r="K46" s="18" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="67.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5255,8 +5255,8 @@
       <c r="J47" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="K47" s="16" t="s">
-        <v>106</v>
+      <c r="K47" s="18" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5325,8 +5325,8 @@
       <c r="J49" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="K49" s="16" t="s">
-        <v>106</v>
+      <c r="K49" s="18" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5431,7 +5431,7 @@
         <v>288</v>
       </c>
       <c r="K52" s="18" t="s">
-        <v>106</v>
+        <v>721</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="54.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5989,7 +5989,7 @@
       <formula>"Yüksek"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K47:K65 K4:K45">
+  <conditionalFormatting sqref="K4:K65">
     <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"Tamamlandı"</formula>
     </cfRule>
@@ -6001,7 +6001,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" promptTitle="Durum" prompt="Yapılacak / Devam Ediyor / Tamamlandı / Bloke" sqref="K47:K65 K4:K45" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" promptTitle="Durum" prompt="Yapılacak / Devam Ediyor / Tamamlandı / Bloke" sqref="K4:K65" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Yapılacak,Devam Ediyor,Tamamlandı,Bloke"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7770,7 +7770,7 @@
       <c r="G17" s="9"/>
     </row>
     <row r="19" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="38" t="s">
         <v>615</v>
       </c>
       <c r="B19" s="33"/>
@@ -7781,7 +7781,7 @@
       <c r="G19" s="33"/>
     </row>
     <row r="20" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="38" t="s">
         <v>616</v>
       </c>
       <c r="B20" s="33"/>
@@ -7792,7 +7792,7 @@
       <c r="G20" s="33"/>
     </row>
     <row r="21" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="38" t="s">
         <v>617</v>
       </c>
       <c r="B21" s="33"/>
